--- a/research/traditional_assets/database/data/nigeria/nigeria_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1342870930483013</v>
+        <v>0.1339157317691564</v>
       </c>
       <c r="C2">
-        <v>47.77343308869061</v>
+        <v>47.50154364490508</v>
       </c>
       <c r="D2">
-        <v>40.36343308869061</v>
+        <v>40.53354364490508</v>
       </c>
       <c r="E2">
-        <v>-18.9</v>
+        <v>-18.458</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4420000000000001</v>
       </c>
       <c r="G2">
         <v>7.41</v>
@@ -1451,28 +1451,28 @@
         <v>13.375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0222326</v>
       </c>
       <c r="N2">
-        <v>13.375</v>
+        <v>13.3527674</v>
       </c>
       <c r="O2">
-        <v>4.0125</v>
+        <v>4.00583022</v>
       </c>
       <c r="P2">
-        <v>9.362500000000001</v>
+        <v>9.346937179999999</v>
       </c>
       <c r="Q2">
-        <v>12.3625</v>
+        <v>12.34693718</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1342870930483013</v>
+        <v>0.1349127593627843</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6213335955608404</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>601.5940555760459</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1339157317691564</v>
+        <v>0.1335443704900115</v>
       </c>
       <c r="C3">
-        <v>47.50154364490508</v>
+        <v>47.23109412195775</v>
       </c>
       <c r="D3">
-        <v>40.53354364490508</v>
+        <v>40.70509412195775</v>
       </c>
       <c r="E3">
-        <v>-18.458</v>
+        <v>-18.016</v>
       </c>
       <c r="F3">
-        <v>0.4420000000000001</v>
+        <v>0.8840000000000001</v>
       </c>
       <c r="G3">
         <v>7.41</v>
@@ -1533,28 +1533,28 @@
         <v>13.375</v>
       </c>
       <c r="M3">
-        <v>0.0222326</v>
+        <v>0.0444652</v>
       </c>
       <c r="N3">
-        <v>13.3527674</v>
+        <v>13.3305348</v>
       </c>
       <c r="O3">
-        <v>4.00583022</v>
+        <v>3.99916044</v>
       </c>
       <c r="P3">
-        <v>9.346937179999999</v>
+        <v>9.331374360000002</v>
       </c>
       <c r="Q3">
-        <v>12.34693718</v>
+        <v>12.33137436</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1349127593627843</v>
+        <v>0.1355511943775628</v>
       </c>
       <c r="T3">
-        <v>0.6213335955608404</v>
+        <v>0.6257850470263859</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>601.5940555760459</v>
+        <v>300.797027788023</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1335443704900115</v>
+        <v>0.1331730092108666</v>
       </c>
       <c r="C4">
-        <v>47.23109412195775</v>
+        <v>46.96210288012424</v>
       </c>
       <c r="D4">
-        <v>40.70509412195775</v>
+        <v>40.87810288012425</v>
       </c>
       <c r="E4">
-        <v>-18.016</v>
+        <v>-17.574</v>
       </c>
       <c r="F4">
-        <v>0.8840000000000001</v>
+        <v>1.326</v>
       </c>
       <c r="G4">
         <v>7.41</v>
@@ -1615,28 +1615,28 @@
         <v>13.375</v>
       </c>
       <c r="M4">
-        <v>0.0444652</v>
+        <v>0.0666978</v>
       </c>
       <c r="N4">
-        <v>13.3305348</v>
+        <v>13.3083022</v>
       </c>
       <c r="O4">
-        <v>3.99916044</v>
+        <v>3.99249066</v>
       </c>
       <c r="P4">
-        <v>9.331374360000002</v>
+        <v>9.31581154</v>
       </c>
       <c r="Q4">
-        <v>12.33137436</v>
+        <v>12.31581154</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1355511943775628</v>
+        <v>0.1362027930008934</v>
       </c>
       <c r="T4">
-        <v>0.6257850470263859</v>
+        <v>0.6303282809963757</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>300.797027788023</v>
+        <v>200.531351858682</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1331730092108666</v>
+        <v>0.1328016479317217</v>
       </c>
       <c r="C5">
-        <v>46.96210288012424</v>
+        <v>46.69458859315918</v>
       </c>
       <c r="D5">
-        <v>40.87810288012425</v>
+        <v>41.05258859315918</v>
       </c>
       <c r="E5">
-        <v>-17.574</v>
+        <v>-17.132</v>
       </c>
       <c r="F5">
-        <v>1.326</v>
+        <v>1.768</v>
       </c>
       <c r="G5">
         <v>7.41</v>
@@ -1697,28 +1697,28 @@
         <v>13.375</v>
       </c>
       <c r="M5">
-        <v>0.0666978</v>
+        <v>0.08893040000000001</v>
       </c>
       <c r="N5">
-        <v>13.3083022</v>
+        <v>13.2860696</v>
       </c>
       <c r="O5">
-        <v>3.99249066</v>
+        <v>3.985820879999999</v>
       </c>
       <c r="P5">
-        <v>9.31581154</v>
+        <v>9.300248719999999</v>
       </c>
       <c r="Q5">
-        <v>12.31581154</v>
+        <v>12.30024872</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1362027930008934</v>
+        <v>0.1368679665955435</v>
       </c>
       <c r="T5">
-        <v>0.6303282809963757</v>
+        <v>0.6349661656740735</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>200.531351858682</v>
+        <v>150.3985138940115</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1328016479317217</v>
+        <v>0.1324302866525768</v>
       </c>
       <c r="C6">
-        <v>46.69458859315918</v>
+        <v>46.42857025501498</v>
       </c>
       <c r="D6">
-        <v>41.05258859315918</v>
+        <v>41.22857025501499</v>
       </c>
       <c r="E6">
-        <v>-17.132</v>
+        <v>-16.69</v>
       </c>
       <c r="F6">
-        <v>1.768</v>
+        <v>2.21</v>
       </c>
       <c r="G6">
         <v>7.41</v>
@@ -1779,28 +1779,28 @@
         <v>13.375</v>
       </c>
       <c r="M6">
-        <v>0.08893040000000001</v>
+        <v>0.111163</v>
       </c>
       <c r="N6">
-        <v>13.2860696</v>
+        <v>13.263837</v>
       </c>
       <c r="O6">
-        <v>3.985820879999999</v>
+        <v>3.9791511</v>
       </c>
       <c r="P6">
-        <v>9.300248719999999</v>
+        <v>9.284685899999999</v>
       </c>
       <c r="Q6">
-        <v>12.30024872</v>
+        <v>12.2846859</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1368679665955435</v>
+        <v>0.1375471438448177</v>
       </c>
       <c r="T6">
-        <v>0.6349661656740735</v>
+        <v>0.6397016900291966</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>150.3985138940115</v>
+        <v>120.3188111152092</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1324302866525768</v>
+        <v>0.1320589253734319</v>
       </c>
       <c r="C7">
-        <v>46.42857025501498</v>
+        <v>46.16406718673464</v>
       </c>
       <c r="D7">
-        <v>41.22857025501499</v>
+        <v>41.40606718673464</v>
       </c>
       <c r="E7">
-        <v>-16.69</v>
+        <v>-16.248</v>
       </c>
       <c r="F7">
-        <v>2.21</v>
+        <v>2.652000000000001</v>
       </c>
       <c r="G7">
         <v>7.41</v>
@@ -1861,28 +1861,28 @@
         <v>13.375</v>
       </c>
       <c r="M7">
-        <v>0.111163</v>
+        <v>0.1333956</v>
       </c>
       <c r="N7">
-        <v>13.263837</v>
+        <v>13.2416044</v>
       </c>
       <c r="O7">
-        <v>3.9791511</v>
+        <v>3.97248132</v>
       </c>
       <c r="P7">
-        <v>9.284685899999999</v>
+        <v>9.26912308</v>
       </c>
       <c r="Q7">
-        <v>12.2846859</v>
+        <v>12.26912308</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1375471438448177</v>
+        <v>0.1382407716738637</v>
       </c>
       <c r="T7">
-        <v>0.6397016900291966</v>
+        <v>0.6445379702216627</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>120.3188111152092</v>
+        <v>100.265675929341</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1320589253734319</v>
+        <v>0.131687564094287</v>
       </c>
       <c r="C8">
-        <v>46.16406718673464</v>
+        <v>45.90109904352295</v>
       </c>
       <c r="D8">
-        <v>41.40606718673464</v>
+        <v>41.58509904352295</v>
       </c>
       <c r="E8">
-        <v>-16.248</v>
+        <v>-15.806</v>
       </c>
       <c r="F8">
-        <v>2.652</v>
+        <v>3.094</v>
       </c>
       <c r="G8">
         <v>7.41</v>
@@ -1943,28 +1943,28 @@
         <v>13.375</v>
       </c>
       <c r="M8">
-        <v>0.1333956</v>
+        <v>0.1556282</v>
       </c>
       <c r="N8">
-        <v>13.2416044</v>
+        <v>13.2193718</v>
       </c>
       <c r="O8">
-        <v>3.97248132</v>
+        <v>3.96581154</v>
       </c>
       <c r="P8">
-        <v>9.26912308</v>
+        <v>9.25356026</v>
       </c>
       <c r="Q8">
-        <v>12.26912308</v>
+        <v>12.25356026</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1382407716738637</v>
+        <v>0.1389493162304161</v>
       </c>
       <c r="T8">
-        <v>0.6445379702216627</v>
+        <v>0.6494782564397733</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>100.265675929341</v>
+        <v>85.94200793943514</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.131687564094287</v>
+        <v>0.1313162028151421</v>
       </c>
       <c r="C9">
-        <v>45.90109904352295</v>
+        <v>45.63968582200224</v>
       </c>
       <c r="D9">
-        <v>41.58509904352295</v>
+        <v>41.76568582200224</v>
       </c>
       <c r="E9">
-        <v>-15.806</v>
+        <v>-15.364</v>
       </c>
       <c r="F9">
-        <v>3.094</v>
+        <v>3.536</v>
       </c>
       <c r="G9">
         <v>7.41</v>
@@ -2025,28 +2025,28 @@
         <v>13.375</v>
       </c>
       <c r="M9">
-        <v>0.1556282</v>
+        <v>0.1778608</v>
       </c>
       <c r="N9">
-        <v>13.2193718</v>
+        <v>13.1971392</v>
       </c>
       <c r="O9">
-        <v>3.96581154</v>
+        <v>3.95914176</v>
       </c>
       <c r="P9">
-        <v>9.25356026</v>
+        <v>9.237997440000001</v>
       </c>
       <c r="Q9">
-        <v>12.25356026</v>
+        <v>12.23799744</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1389493162304161</v>
+        <v>0.1396732639295023</v>
       </c>
       <c r="T9">
-        <v>0.6494782564397733</v>
+        <v>0.6545259401843646</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>85.94200793943514</v>
+        <v>75.19925694700575</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1313162028151421</v>
+        <v>0.1309448415359972</v>
       </c>
       <c r="C10">
-        <v>45.63968582200224</v>
+        <v>45.37984786765789</v>
       </c>
       <c r="D10">
-        <v>41.76568582200224</v>
+        <v>41.94784786765789</v>
       </c>
       <c r="E10">
-        <v>-15.364</v>
+        <v>-14.922</v>
       </c>
       <c r="F10">
-        <v>3.536</v>
+        <v>3.978</v>
       </c>
       <c r="G10">
         <v>7.41</v>
@@ -2107,28 +2107,28 @@
         <v>13.375</v>
       </c>
       <c r="M10">
-        <v>0.1778608</v>
+        <v>0.2000934</v>
       </c>
       <c r="N10">
-        <v>13.1971392</v>
+        <v>13.1749066</v>
       </c>
       <c r="O10">
-        <v>3.95914176</v>
+        <v>3.95247198</v>
       </c>
       <c r="P10">
-        <v>9.237997440000001</v>
+        <v>9.22243462</v>
       </c>
       <c r="Q10">
-        <v>12.23799744</v>
+        <v>12.22243462</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1396732639295023</v>
+        <v>0.1404131225670299</v>
       </c>
       <c r="T10">
-        <v>0.6545259401843646</v>
+        <v>0.6596845620332324</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>75.19925694700575</v>
+        <v>66.843783952894</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1309448415359972</v>
+        <v>0.1305734802568523</v>
       </c>
       <c r="C11">
-        <v>45.37984786765789</v>
+        <v>45.1216058824794</v>
       </c>
       <c r="D11">
-        <v>41.94784786765789</v>
+        <v>42.13160588247941</v>
       </c>
       <c r="E11">
-        <v>-14.922</v>
+        <v>-14.48</v>
       </c>
       <c r="F11">
-        <v>3.978</v>
+        <v>4.42</v>
       </c>
       <c r="G11">
         <v>7.41</v>
@@ -2189,28 +2189,28 @@
         <v>13.375</v>
       </c>
       <c r="M11">
-        <v>0.2000934</v>
+        <v>0.222326</v>
       </c>
       <c r="N11">
-        <v>13.1749066</v>
+        <v>13.152674</v>
       </c>
       <c r="O11">
-        <v>3.95247198</v>
+        <v>3.9458022</v>
       </c>
       <c r="P11">
-        <v>9.22243462</v>
+        <v>9.2068718</v>
       </c>
       <c r="Q11">
-        <v>12.22243462</v>
+        <v>12.2068718</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1404131225670299</v>
+        <v>0.1411694225076137</v>
       </c>
       <c r="T11">
-        <v>0.6596845620332324</v>
+        <v>0.6649578199231864</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>66.843783952894</v>
+        <v>60.15940555760459</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1305734802568523</v>
+        <v>0.1302021189777074</v>
       </c>
       <c r="C12">
-        <v>45.1216058824794</v>
+        <v>44.86498093280343</v>
       </c>
       <c r="D12">
-        <v>42.13160588247941</v>
+        <v>42.31698093280343</v>
       </c>
       <c r="E12">
-        <v>-14.48</v>
+        <v>-14.038</v>
       </c>
       <c r="F12">
-        <v>4.420000000000001</v>
+        <v>4.862</v>
       </c>
       <c r="G12">
         <v>7.41</v>
@@ -2271,28 +2271,28 @@
         <v>13.375</v>
       </c>
       <c r="M12">
-        <v>0.222326</v>
+        <v>0.2445586</v>
       </c>
       <c r="N12">
-        <v>13.152674</v>
+        <v>13.1304414</v>
       </c>
       <c r="O12">
-        <v>3.9458022</v>
+        <v>3.93913242</v>
       </c>
       <c r="P12">
-        <v>9.2068718</v>
+        <v>9.191308980000001</v>
       </c>
       <c r="Q12">
-        <v>12.2068718</v>
+        <v>12.19130898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1411694225076137</v>
+        <v>0.1419427179524802</v>
       </c>
       <c r="T12">
-        <v>0.6649578199231864</v>
+        <v>0.6703495779904426</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>60.15940555760459</v>
+        <v>54.69036868873146</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1302021189777074</v>
+        <v>0.1298307576985625</v>
       </c>
       <c r="C13">
-        <v>44.86498093280343</v>
+        <v>44.60999445736462</v>
       </c>
       <c r="D13">
-        <v>42.31698093280343</v>
+        <v>42.50399445736463</v>
       </c>
       <c r="E13">
-        <v>-14.038</v>
+        <v>-13.596</v>
       </c>
       <c r="F13">
-        <v>4.862</v>
+        <v>5.304</v>
       </c>
       <c r="G13">
         <v>7.41</v>
@@ -2353,28 +2353,28 @@
         <v>13.375</v>
       </c>
       <c r="M13">
-        <v>0.2445586</v>
+        <v>0.2667912</v>
       </c>
       <c r="N13">
-        <v>13.1304414</v>
+        <v>13.1082088</v>
       </c>
       <c r="O13">
-        <v>3.93913242</v>
+        <v>3.93246264</v>
       </c>
       <c r="P13">
-        <v>9.191308980000001</v>
+        <v>9.175746159999999</v>
       </c>
       <c r="Q13">
-        <v>12.19130898</v>
+        <v>12.17574616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1419427179524802</v>
+        <v>0.142733588293821</v>
       </c>
       <c r="T13">
-        <v>0.6703495779904426</v>
+        <v>0.6758638760137728</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>54.69036868873146</v>
+        <v>50.1328379646705</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1298307576985625</v>
+        <v>0.1294593964194176</v>
       </c>
       <c r="C14">
-        <v>44.60999445736462</v>
+        <v>44.356668275561</v>
       </c>
       <c r="D14">
-        <v>42.50399445736463</v>
+        <v>42.692668275561</v>
       </c>
       <c r="E14">
-        <v>-13.596</v>
+        <v>-13.154</v>
       </c>
       <c r="F14">
-        <v>5.304</v>
+        <v>5.746</v>
       </c>
       <c r="G14">
         <v>7.41</v>
@@ -2435,28 +2435,28 @@
         <v>13.375</v>
       </c>
       <c r="M14">
-        <v>0.2667912</v>
+        <v>0.2890238</v>
       </c>
       <c r="N14">
-        <v>13.1082088</v>
+        <v>13.0859762</v>
       </c>
       <c r="O14">
-        <v>3.93246264</v>
+        <v>3.92579286</v>
       </c>
       <c r="P14">
-        <v>9.175746159999999</v>
+        <v>9.16018334</v>
       </c>
       <c r="Q14">
-        <v>12.17574616</v>
+        <v>12.16018334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.142733588293821</v>
+        <v>0.143542639562549</v>
       </c>
       <c r="T14">
-        <v>0.6758638760137728</v>
+        <v>0.6815049395089038</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>50.1328379646705</v>
+        <v>46.276465813542</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1294593964194176</v>
+        <v>0.1290880351402727</v>
       </c>
       <c r="C15">
-        <v>44.356668275561</v>
+        <v>44.10502459594026</v>
       </c>
       <c r="D15">
-        <v>42.692668275561</v>
+        <v>42.88302459594027</v>
       </c>
       <c r="E15">
-        <v>-13.154</v>
+        <v>-12.712</v>
       </c>
       <c r="F15">
-        <v>5.746</v>
+        <v>6.188000000000001</v>
       </c>
       <c r="G15">
         <v>7.41</v>
@@ -2517,28 +2517,28 @@
         <v>13.375</v>
       </c>
       <c r="M15">
-        <v>0.2890238</v>
+        <v>0.3112564</v>
       </c>
       <c r="N15">
-        <v>13.0859762</v>
+        <v>13.0637436</v>
       </c>
       <c r="O15">
-        <v>3.92579286</v>
+        <v>3.91912308</v>
       </c>
       <c r="P15">
-        <v>9.16018334</v>
+        <v>9.14462052</v>
       </c>
       <c r="Q15">
-        <v>12.16018334</v>
+        <v>12.14462052</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.143542639562549</v>
+        <v>0.1443705059770612</v>
       </c>
       <c r="T15">
-        <v>0.6815049395089038</v>
+        <v>0.6872771905271773</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>46.276465813542</v>
+        <v>42.97100396971757</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1290880351402727</v>
+        <v>0.1287166738611278</v>
       </c>
       <c r="C16">
-        <v>44.10502459594026</v>
+        <v>43.85508602491439</v>
       </c>
       <c r="D16">
-        <v>42.88302459594027</v>
+        <v>43.07508602491439</v>
       </c>
       <c r="E16">
-        <v>-12.712</v>
+        <v>-12.27</v>
       </c>
       <c r="F16">
-        <v>6.188000000000001</v>
+        <v>6.630000000000002</v>
       </c>
       <c r="G16">
         <v>7.41</v>
@@ -2599,28 +2599,28 @@
         <v>13.375</v>
       </c>
       <c r="M16">
-        <v>0.3112564</v>
+        <v>0.3334890000000001</v>
       </c>
       <c r="N16">
-        <v>13.0637436</v>
+        <v>13.041511</v>
       </c>
       <c r="O16">
-        <v>3.91912308</v>
+        <v>3.9124533</v>
       </c>
       <c r="P16">
-        <v>9.14462052</v>
+        <v>9.129057700000001</v>
       </c>
       <c r="Q16">
-        <v>12.14462052</v>
+        <v>12.1290577</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1443705059770612</v>
+        <v>0.1452178516013268</v>
       </c>
       <c r="T16">
-        <v>0.6872771905271773</v>
+        <v>0.693185259216469</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>42.97100396971757</v>
+        <v>40.10627037173639</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1287166738611278</v>
+        <v>0.1283453125819829</v>
       </c>
       <c r="C17">
-        <v>43.85508602491439</v>
+        <v>43.60687557570932</v>
       </c>
       <c r="D17">
-        <v>43.07508602491439</v>
+        <v>43.26887557570932</v>
       </c>
       <c r="E17">
-        <v>-12.27</v>
+        <v>-11.828</v>
       </c>
       <c r="F17">
-        <v>6.63</v>
+        <v>7.072000000000001</v>
       </c>
       <c r="G17">
         <v>7.41</v>
@@ -2681,28 +2681,28 @@
         <v>13.375</v>
       </c>
       <c r="M17">
-        <v>0.333489</v>
+        <v>0.3557216</v>
       </c>
       <c r="N17">
-        <v>13.041511</v>
+        <v>13.0192784</v>
       </c>
       <c r="O17">
-        <v>3.9124533</v>
+        <v>3.90578352</v>
       </c>
       <c r="P17">
-        <v>9.129057700000001</v>
+        <v>9.113494879999999</v>
       </c>
       <c r="Q17">
-        <v>12.1290577</v>
+        <v>12.11349488</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1452178516013268</v>
+        <v>0.1460853721214082</v>
       </c>
       <c r="T17">
-        <v>0.693185259216469</v>
+        <v>0.6992339962078867</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>40.1062703717364</v>
+        <v>37.59962847350287</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1283453125819829</v>
+        <v>0.127973951302838</v>
       </c>
       <c r="C18">
-        <v>43.60687557570932</v>
+        <v>43.36041667755726</v>
       </c>
       <c r="D18">
-        <v>43.26887557570932</v>
+        <v>43.46441667755727</v>
       </c>
       <c r="E18">
-        <v>-11.828</v>
+        <v>-11.386</v>
       </c>
       <c r="F18">
-        <v>7.072000000000001</v>
+        <v>7.514000000000001</v>
       </c>
       <c r="G18">
         <v>7.41</v>
@@ -2763,28 +2763,28 @@
         <v>13.375</v>
       </c>
       <c r="M18">
-        <v>0.3557216</v>
+        <v>0.3779542</v>
       </c>
       <c r="N18">
-        <v>13.0192784</v>
+        <v>12.9970458</v>
       </c>
       <c r="O18">
-        <v>3.90578352</v>
+        <v>3.89911374</v>
       </c>
       <c r="P18">
-        <v>9.113494879999999</v>
+        <v>9.097932060000002</v>
       </c>
       <c r="Q18">
-        <v>12.11349488</v>
+        <v>12.09793206</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1460853721214082</v>
+        <v>0.1469737967504072</v>
       </c>
       <c r="T18">
-        <v>0.6992339962078867</v>
+        <v>0.7054284858978929</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>37.59962847350287</v>
+        <v>35.38788562212035</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.127973951302838</v>
+        <v>0.1276025900236931</v>
       </c>
       <c r="C19">
-        <v>43.36041667755726</v>
+        <v>43.11573318513962</v>
       </c>
       <c r="D19">
-        <v>43.46441667755727</v>
+        <v>43.66173318513962</v>
       </c>
       <c r="E19">
-        <v>-11.386</v>
+        <v>-10.944</v>
       </c>
       <c r="F19">
-        <v>7.514000000000001</v>
+        <v>7.956000000000001</v>
       </c>
       <c r="G19">
         <v>7.41</v>
@@ -2845,28 +2845,28 @@
         <v>13.375</v>
       </c>
       <c r="M19">
-        <v>0.3779542</v>
+        <v>0.4001868000000001</v>
       </c>
       <c r="N19">
-        <v>12.9970458</v>
+        <v>12.9748132</v>
       </c>
       <c r="O19">
-        <v>3.89911374</v>
+        <v>3.89244396</v>
       </c>
       <c r="P19">
-        <v>9.097932060000002</v>
+        <v>9.08236924</v>
       </c>
       <c r="Q19">
-        <v>12.09793206</v>
+        <v>12.08236924</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1469737967504072</v>
+        <v>0.1478838902727964</v>
       </c>
       <c r="T19">
-        <v>0.7054284858978929</v>
+        <v>0.7117740607022892</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>35.38788562212035</v>
+        <v>33.42189197644699</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1276025900236931</v>
+        <v>0.1272312287445482</v>
       </c>
       <c r="C20">
-        <v>43.11573318513962</v>
+        <v>42.87284938828792</v>
       </c>
       <c r="D20">
-        <v>43.66173318513962</v>
+        <v>43.86084938828793</v>
       </c>
       <c r="E20">
-        <v>-10.944</v>
+        <v>-10.502</v>
       </c>
       <c r="F20">
-        <v>7.956</v>
+        <v>8.398000000000001</v>
       </c>
       <c r="G20">
         <v>7.41</v>
@@ -2927,28 +2927,28 @@
         <v>13.375</v>
       </c>
       <c r="M20">
-        <v>0.4001868</v>
+        <v>0.4224194000000001</v>
       </c>
       <c r="N20">
-        <v>12.9748132</v>
+        <v>12.9525806</v>
       </c>
       <c r="O20">
-        <v>3.89244396</v>
+        <v>3.885774179999999</v>
       </c>
       <c r="P20">
-        <v>9.08236924</v>
+        <v>9.066806419999999</v>
       </c>
       <c r="Q20">
-        <v>12.08236924</v>
+        <v>12.06680642</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1478838902727964</v>
+        <v>0.1488164552401829</v>
       </c>
       <c r="T20">
-        <v>0.7117740607022892</v>
+        <v>0.7182763163660535</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>33.421891976447</v>
+        <v>31.66284503031821</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1272312287445482</v>
+        <v>0.1268598674654033</v>
       </c>
       <c r="C21">
-        <v>42.87284938828792</v>
+        <v>42.63179002195191</v>
       </c>
       <c r="D21">
-        <v>43.86084938828793</v>
+        <v>44.06179002195191</v>
       </c>
       <c r="E21">
-        <v>-10.502</v>
+        <v>-10.06</v>
       </c>
       <c r="F21">
-        <v>8.398000000000001</v>
+        <v>8.840000000000002</v>
       </c>
       <c r="G21">
         <v>7.41</v>
@@ -3009,28 +3009,28 @@
         <v>13.375</v>
       </c>
       <c r="M21">
-        <v>0.4224194000000001</v>
+        <v>0.444652</v>
       </c>
       <c r="N21">
-        <v>12.9525806</v>
+        <v>12.930348</v>
       </c>
       <c r="O21">
-        <v>3.885774179999999</v>
+        <v>3.8791044</v>
       </c>
       <c r="P21">
-        <v>9.066806419999999</v>
+        <v>9.051243599999999</v>
       </c>
       <c r="Q21">
-        <v>12.06680642</v>
+        <v>12.0512436</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1488164552401829</v>
+        <v>0.1497723343317541</v>
       </c>
       <c r="T21">
-        <v>0.7182763163660535</v>
+        <v>0.724941128421412</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>31.66284503031821</v>
+        <v>30.0797027788023</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1268598674654033</v>
+        <v>0.1264885061862584</v>
       </c>
       <c r="C22">
-        <v>42.63179002195191</v>
+        <v>42.39258027644237</v>
       </c>
       <c r="D22">
-        <v>44.06179002195191</v>
+        <v>44.26458027644237</v>
       </c>
       <c r="E22">
-        <v>-10.06</v>
+        <v>-9.617999999999997</v>
       </c>
       <c r="F22">
-        <v>8.840000000000002</v>
+        <v>9.282000000000002</v>
       </c>
       <c r="G22">
         <v>7.41</v>
@@ -3091,28 +3091,28 @@
         <v>13.375</v>
       </c>
       <c r="M22">
-        <v>0.444652</v>
+        <v>0.4668846000000001</v>
       </c>
       <c r="N22">
-        <v>12.930348</v>
+        <v>12.9081154</v>
       </c>
       <c r="O22">
-        <v>3.8791044</v>
+        <v>3.87243462</v>
       </c>
       <c r="P22">
-        <v>9.051243599999999</v>
+        <v>9.03568078</v>
       </c>
       <c r="Q22">
-        <v>12.0512436</v>
+        <v>12.03568078</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1497723343317541</v>
+        <v>0.1507524128939979</v>
       </c>
       <c r="T22">
-        <v>0.724941128421412</v>
+        <v>0.7317746698958935</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>30.0797027788023</v>
+        <v>28.64733597981171</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1264885061862583</v>
+        <v>0.1261171449071135</v>
       </c>
       <c r="C23">
-        <v>42.39258027644239</v>
+        <v>42.15524580795849</v>
       </c>
       <c r="D23">
-        <v>44.26458027644238</v>
+        <v>44.4692458079585</v>
       </c>
       <c r="E23">
-        <v>-9.617999999999999</v>
+        <v>-9.175999999999998</v>
       </c>
       <c r="F23">
-        <v>9.282</v>
+        <v>9.724</v>
       </c>
       <c r="G23">
         <v>7.41</v>
@@ -3173,28 +3173,28 @@
         <v>13.375</v>
       </c>
       <c r="M23">
-        <v>0.4668846</v>
+        <v>0.4891172</v>
       </c>
       <c r="N23">
-        <v>12.9081154</v>
+        <v>12.8858828</v>
       </c>
       <c r="O23">
-        <v>3.87243462</v>
+        <v>3.86576484</v>
       </c>
       <c r="P23">
-        <v>9.03568078</v>
+        <v>9.02011796</v>
       </c>
       <c r="Q23">
-        <v>12.03568078</v>
+        <v>12.02011796</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1507524128939979</v>
+        <v>0.1517576216757865</v>
       </c>
       <c r="T23">
-        <v>0.7317746698958932</v>
+        <v>0.7387834303825409</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>28.64733597981171</v>
+        <v>27.34518434436573</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1261171449071135</v>
+        <v>0.1257457836279685</v>
       </c>
       <c r="C24">
-        <v>42.15524580795849</v>
+        <v>41.91981274940851</v>
       </c>
       <c r="D24">
-        <v>44.4692458079585</v>
+        <v>44.6758127494085</v>
       </c>
       <c r="E24">
-        <v>-9.175999999999998</v>
+        <v>-8.733999999999998</v>
       </c>
       <c r="F24">
-        <v>9.724</v>
+        <v>10.166</v>
       </c>
       <c r="G24">
         <v>7.41</v>
@@ -3255,28 +3255,28 @@
         <v>13.375</v>
       </c>
       <c r="M24">
-        <v>0.4891172</v>
+        <v>0.5113498</v>
       </c>
       <c r="N24">
-        <v>12.8858828</v>
+        <v>12.8636502</v>
       </c>
       <c r="O24">
-        <v>3.86576484</v>
+        <v>3.85909506</v>
       </c>
       <c r="P24">
-        <v>9.02011796</v>
+        <v>9.004555140000001</v>
       </c>
       <c r="Q24">
-        <v>12.02011796</v>
+        <v>12.00455514</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1517576216757865</v>
+        <v>0.1527889397765825</v>
       </c>
       <c r="T24">
-        <v>0.7387834303825409</v>
+        <v>0.7459742365961144</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>27.34518434436573</v>
+        <v>26.15626328591505</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1257457836279685</v>
+        <v>0.1253744223488236</v>
       </c>
       <c r="C25">
-        <v>41.91981274940851</v>
+        <v>41.68630772153321</v>
       </c>
       <c r="D25">
-        <v>44.6758127494085</v>
+        <v>44.88430772153321</v>
       </c>
       <c r="E25">
-        <v>-8.733999999999998</v>
+        <v>-8.291999999999996</v>
       </c>
       <c r="F25">
-        <v>10.166</v>
+        <v>10.608</v>
       </c>
       <c r="G25">
         <v>7.41</v>
@@ -3337,28 +3337,28 @@
         <v>13.375</v>
       </c>
       <c r="M25">
-        <v>0.5113498</v>
+        <v>0.5335824000000001</v>
       </c>
       <c r="N25">
-        <v>12.8636502</v>
+        <v>12.8414176</v>
       </c>
       <c r="O25">
-        <v>3.85909506</v>
+        <v>3.85242528</v>
       </c>
       <c r="P25">
-        <v>9.004555140000001</v>
+        <v>8.988992319999999</v>
       </c>
       <c r="Q25">
-        <v>12.00455514</v>
+        <v>11.98899232</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1527889397765825</v>
+        <v>0.1538473978273995</v>
       </c>
       <c r="T25">
-        <v>0.7459742365961144</v>
+        <v>0.7533542745521504</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>26.15626328591505</v>
+        <v>25.06641898233524</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1253744223488236</v>
+        <v>0.1250030610696787</v>
       </c>
       <c r="C26">
-        <v>41.68630772153321</v>
+        <v>41.45475784434272</v>
       </c>
       <c r="D26">
-        <v>44.88430772153321</v>
+        <v>45.09475784434272</v>
       </c>
       <c r="E26">
-        <v>-8.291999999999998</v>
+        <v>-7.849999999999998</v>
       </c>
       <c r="F26">
-        <v>10.608</v>
+        <v>11.05</v>
       </c>
       <c r="G26">
         <v>7.41</v>
@@ -3419,28 +3419,28 @@
         <v>13.375</v>
       </c>
       <c r="M26">
-        <v>0.5335824</v>
+        <v>0.5558150000000001</v>
       </c>
       <c r="N26">
-        <v>12.8414176</v>
+        <v>12.819185</v>
       </c>
       <c r="O26">
-        <v>3.85242528</v>
+        <v>3.8457555</v>
       </c>
       <c r="P26">
-        <v>8.988992319999999</v>
+        <v>8.9734295</v>
       </c>
       <c r="Q26">
-        <v>11.98899232</v>
+        <v>11.9734295</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1538473978273995</v>
+        <v>0.1549340814262383</v>
       </c>
       <c r="T26">
-        <v>0.7533542745521504</v>
+        <v>0.7609311135203474</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>25.06641898233525</v>
+        <v>24.06376222304183</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1250030610696787</v>
+        <v>0.1246316997905338</v>
       </c>
       <c r="C27">
-        <v>41.45475784434272</v>
+        <v>41.22519074887607</v>
       </c>
       <c r="D27">
-        <v>45.09475784434272</v>
+        <v>45.30719074887608</v>
       </c>
       <c r="E27">
-        <v>-7.849999999999998</v>
+        <v>-7.407999999999998</v>
       </c>
       <c r="F27">
-        <v>11.05</v>
+        <v>11.492</v>
       </c>
       <c r="G27">
         <v>7.41</v>
@@ -3501,28 +3501,28 @@
         <v>13.375</v>
       </c>
       <c r="M27">
-        <v>0.5558150000000001</v>
+        <v>0.5780476</v>
       </c>
       <c r="N27">
-        <v>12.819185</v>
+        <v>12.7969524</v>
       </c>
       <c r="O27">
-        <v>3.8457555</v>
+        <v>3.83908572</v>
       </c>
       <c r="P27">
-        <v>8.9734295</v>
+        <v>8.95786668</v>
       </c>
       <c r="Q27">
-        <v>11.9734295</v>
+        <v>11.95786668</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1549340814262383</v>
+        <v>0.1560501348520727</v>
       </c>
       <c r="T27">
-        <v>0.7609311135203474</v>
+        <v>0.768712731920117</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>24.06376222304183</v>
+        <v>23.138232906771</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1246316997905338</v>
+        <v>0.1242603385113889</v>
       </c>
       <c r="C28">
-        <v>41.22519074887607</v>
+        <v>40.99763458929517</v>
       </c>
       <c r="D28">
-        <v>45.30719074887608</v>
+        <v>45.52163458929517</v>
       </c>
       <c r="E28">
-        <v>-7.407999999999998</v>
+        <v>-6.965999999999998</v>
       </c>
       <c r="F28">
-        <v>11.492</v>
+        <v>11.934</v>
       </c>
       <c r="G28">
         <v>7.41</v>
@@ -3583,28 +3583,28 @@
         <v>13.375</v>
       </c>
       <c r="M28">
-        <v>0.5780476</v>
+        <v>0.6002802</v>
       </c>
       <c r="N28">
-        <v>12.7969524</v>
+        <v>12.7747198</v>
       </c>
       <c r="O28">
-        <v>3.83908572</v>
+        <v>3.83241594</v>
       </c>
       <c r="P28">
-        <v>8.95786668</v>
+        <v>8.942303859999999</v>
       </c>
       <c r="Q28">
-        <v>11.95786668</v>
+        <v>11.94230386</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1560501348520727</v>
+        <v>0.1571967650840944</v>
       </c>
       <c r="T28">
-        <v>0.768712731920117</v>
+        <v>0.7767075453445382</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>23.138232906771</v>
+        <v>22.28126131763133</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1242603385113889</v>
+        <v>0.123888977232244</v>
       </c>
       <c r="C29">
-        <v>40.99763458929517</v>
+        <v>40.77211805532355</v>
       </c>
       <c r="D29">
-        <v>45.52163458929517</v>
+        <v>45.73811805532355</v>
       </c>
       <c r="E29">
-        <v>-6.965999999999998</v>
+        <v>-6.523999999999997</v>
       </c>
       <c r="F29">
-        <v>11.934</v>
+        <v>12.376</v>
       </c>
       <c r="G29">
         <v>7.41</v>
@@ -3665,28 +3665,28 @@
         <v>13.375</v>
       </c>
       <c r="M29">
-        <v>0.6002802</v>
+        <v>0.6225128</v>
       </c>
       <c r="N29">
-        <v>12.7747198</v>
+        <v>12.7524872</v>
       </c>
       <c r="O29">
-        <v>3.83241594</v>
+        <v>3.82574616</v>
       </c>
       <c r="P29">
-        <v>8.942303859999999</v>
+        <v>8.926741040000001</v>
       </c>
       <c r="Q29">
-        <v>11.94230386</v>
+        <v>11.92674104</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1571967650840944</v>
+        <v>0.1583752461558945</v>
       </c>
       <c r="T29">
-        <v>0.7767075453445382</v>
+        <v>0.7849244369196375</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.28126131763133</v>
+        <v>21.48550198485879</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.123888977232244</v>
+        <v>0.1235176159530991</v>
       </c>
       <c r="C30">
-        <v>40.77211805532355</v>
+        <v>40.54867038504189</v>
       </c>
       <c r="D30">
-        <v>45.73811805532355</v>
+        <v>45.9566703850419</v>
       </c>
       <c r="E30">
-        <v>-6.523999999999997</v>
+        <v>-6.081999999999995</v>
       </c>
       <c r="F30">
-        <v>12.376</v>
+        <v>12.818</v>
       </c>
       <c r="G30">
         <v>7.41</v>
@@ -3747,28 +3747,28 @@
         <v>13.375</v>
       </c>
       <c r="M30">
-        <v>0.6225128</v>
+        <v>0.6447454000000001</v>
       </c>
       <c r="N30">
-        <v>12.7524872</v>
+        <v>12.7302546</v>
       </c>
       <c r="O30">
-        <v>3.82574616</v>
+        <v>3.81907638</v>
       </c>
       <c r="P30">
-        <v>8.926741040000001</v>
+        <v>8.91117822</v>
       </c>
       <c r="Q30">
-        <v>11.92674104</v>
+        <v>11.91117822</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1583752461558945</v>
+        <v>0.1595869238776044</v>
       </c>
       <c r="T30">
-        <v>0.7849244369196375</v>
+        <v>0.7933727902292468</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>21.48550198485879</v>
+        <v>20.74462260607055</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1235176159530991</v>
+        <v>0.1231462546739542</v>
       </c>
       <c r="C31">
-        <v>40.5486703850419</v>
+        <v>40.32732137805213</v>
       </c>
       <c r="D31">
-        <v>45.9566703850419</v>
+        <v>46.17732137805213</v>
       </c>
       <c r="E31">
-        <v>-6.081999999999999</v>
+        <v>-5.639999999999999</v>
       </c>
       <c r="F31">
-        <v>12.818</v>
+        <v>13.26</v>
       </c>
       <c r="G31">
         <v>7.41</v>
@@ -3829,28 +3829,28 @@
         <v>13.375</v>
       </c>
       <c r="M31">
-        <v>0.6447453999999999</v>
+        <v>0.666978</v>
       </c>
       <c r="N31">
-        <v>12.7302546</v>
+        <v>12.708022</v>
       </c>
       <c r="O31">
-        <v>3.81907638</v>
+        <v>3.8124066</v>
       </c>
       <c r="P31">
-        <v>8.91117822</v>
+        <v>8.895615400000001</v>
       </c>
       <c r="Q31">
-        <v>11.91117822</v>
+        <v>11.8956154</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1595869238776044</v>
+        <v>0.1608332209627917</v>
       </c>
       <c r="T31">
-        <v>0.7933727902292468</v>
+        <v>0.8020625250619877</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>20.74462260607055</v>
+        <v>20.0531351858682</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1231462546739542</v>
+        <v>0.1227748933948093</v>
       </c>
       <c r="C32">
-        <v>40.32732137805213</v>
+        <v>40.10810140902252</v>
       </c>
       <c r="D32">
-        <v>46.17732137805213</v>
+        <v>46.40010140902253</v>
       </c>
       <c r="E32">
-        <v>-5.639999999999999</v>
+        <v>-5.197999999999999</v>
       </c>
       <c r="F32">
-        <v>13.26</v>
+        <v>13.702</v>
       </c>
       <c r="G32">
         <v>7.41</v>
@@ -3911,28 +3911,28 @@
         <v>13.375</v>
       </c>
       <c r="M32">
-        <v>0.666978</v>
+        <v>0.6892106</v>
       </c>
       <c r="N32">
-        <v>12.708022</v>
+        <v>12.6857894</v>
       </c>
       <c r="O32">
-        <v>3.8124066</v>
+        <v>3.80573682</v>
       </c>
       <c r="P32">
-        <v>8.895615400000001</v>
+        <v>8.880052580000001</v>
       </c>
       <c r="Q32">
-        <v>11.8956154</v>
+        <v>11.88005258</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1608332209627917</v>
+        <v>0.1621156426011729</v>
       </c>
       <c r="T32">
-        <v>0.8020625250619877</v>
+        <v>0.8110041362666921</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>20.0531351858682</v>
+        <v>19.40625985729181</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1227748933948093</v>
+        <v>0.1224035321156644</v>
       </c>
       <c r="C33">
-        <v>40.10810140902252</v>
+        <v>39.8910414416269</v>
       </c>
       <c r="D33">
-        <v>46.40010140902253</v>
+        <v>46.62504144162691</v>
       </c>
       <c r="E33">
-        <v>-5.197999999999999</v>
+        <v>-4.755999999999997</v>
       </c>
       <c r="F33">
-        <v>13.702</v>
+        <v>14.144</v>
       </c>
       <c r="G33">
         <v>7.41</v>
@@ -3993,28 +3993,28 @@
         <v>13.375</v>
       </c>
       <c r="M33">
-        <v>0.6892106</v>
+        <v>0.7114432000000001</v>
       </c>
       <c r="N33">
-        <v>12.6857894</v>
+        <v>12.6635568</v>
       </c>
       <c r="O33">
-        <v>3.80573682</v>
+        <v>3.79906704</v>
       </c>
       <c r="P33">
-        <v>8.880052580000001</v>
+        <v>8.864489760000001</v>
       </c>
       <c r="Q33">
-        <v>11.88005258</v>
+        <v>11.86448976</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1621156426011729</v>
+        <v>0.1634357825230359</v>
       </c>
       <c r="T33">
-        <v>0.8110041362666921</v>
+        <v>0.8202087360362408</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.40625985729181</v>
+        <v>18.79981423675144</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1224035321156644</v>
+        <v>0.1220321708365195</v>
       </c>
       <c r="C34">
-        <v>39.8910414416269</v>
+        <v>39.67617304289112</v>
       </c>
       <c r="D34">
-        <v>46.62504144162691</v>
+        <v>46.85217304289112</v>
       </c>
       <c r="E34">
-        <v>-4.755999999999997</v>
+        <v>-4.313999999999997</v>
       </c>
       <c r="F34">
-        <v>14.144</v>
+        <v>14.586</v>
       </c>
       <c r="G34">
         <v>7.41</v>
@@ -4075,28 +4075,28 @@
         <v>13.375</v>
       </c>
       <c r="M34">
-        <v>0.7114432000000001</v>
+        <v>0.7336758000000001</v>
       </c>
       <c r="N34">
-        <v>12.6635568</v>
+        <v>12.6413242</v>
       </c>
       <c r="O34">
-        <v>3.79906704</v>
+        <v>3.79239726</v>
       </c>
       <c r="P34">
-        <v>8.864489760000001</v>
+        <v>8.84892694</v>
       </c>
       <c r="Q34">
-        <v>11.86448976</v>
+        <v>11.84892694</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1634357825230359</v>
+        <v>0.1647953296067456</v>
       </c>
       <c r="T34">
-        <v>0.8202087360362408</v>
+        <v>0.829688099978015</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>18.79981423675144</v>
+        <v>18.23012289624382</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1220321708365195</v>
+        <v>0.1216608095573746</v>
       </c>
       <c r="C35">
-        <v>39.67617304289112</v>
+        <v>39.46352839796108</v>
       </c>
       <c r="D35">
-        <v>46.85217304289112</v>
+        <v>47.08152839796109</v>
       </c>
       <c r="E35">
-        <v>-4.313999999999997</v>
+        <v>-3.871999999999996</v>
       </c>
       <c r="F35">
-        <v>14.586</v>
+        <v>15.028</v>
       </c>
       <c r="G35">
         <v>7.41</v>
@@ -4157,28 +4157,28 @@
         <v>13.375</v>
       </c>
       <c r="M35">
-        <v>0.7336758000000001</v>
+        <v>0.7559084</v>
       </c>
       <c r="N35">
-        <v>12.6413242</v>
+        <v>12.6190916</v>
       </c>
       <c r="O35">
-        <v>3.79239726</v>
+        <v>3.78572748</v>
       </c>
       <c r="P35">
-        <v>8.84892694</v>
+        <v>8.833364120000001</v>
       </c>
       <c r="Q35">
-        <v>11.84892694</v>
+        <v>11.83336412</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1647953296067456</v>
+        <v>0.1661960750869312</v>
       </c>
       <c r="T35">
-        <v>0.829688099978015</v>
+        <v>0.8394547173725698</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.23012289624382</v>
+        <v>17.69394281106018</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1216608095573746</v>
+        <v>0.1212894482782297</v>
       </c>
       <c r="C36">
-        <v>39.46352839796108</v>
+        <v>39.25314032530653</v>
       </c>
       <c r="D36">
-        <v>47.08152839796109</v>
+        <v>47.31314032530653</v>
       </c>
       <c r="E36">
-        <v>-3.871999999999996</v>
+        <v>-3.429999999999996</v>
       </c>
       <c r="F36">
-        <v>15.028</v>
+        <v>15.47</v>
       </c>
       <c r="G36">
         <v>7.41</v>
@@ -4239,28 +4239,28 @@
         <v>13.375</v>
       </c>
       <c r="M36">
-        <v>0.7559084</v>
+        <v>0.7781410000000001</v>
       </c>
       <c r="N36">
-        <v>12.6190916</v>
+        <v>12.596859</v>
       </c>
       <c r="O36">
-        <v>3.78572748</v>
+        <v>3.7790577</v>
       </c>
       <c r="P36">
-        <v>8.833364120000001</v>
+        <v>8.817801299999999</v>
       </c>
       <c r="Q36">
-        <v>11.83336412</v>
+        <v>11.8178013</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1661960750869312</v>
+        <v>0.1676399204280457</v>
       </c>
       <c r="T36">
-        <v>0.8394547173725698</v>
+        <v>0.8495218460715728</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>17.69394281106018</v>
+        <v>17.18840158788703</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1212894482782297</v>
+        <v>0.1209180869990848</v>
       </c>
       <c r="C37">
-        <v>39.25314032530653</v>
+        <v>39.04504229237581</v>
       </c>
       <c r="D37">
-        <v>47.31314032530653</v>
+        <v>47.54704229237581</v>
       </c>
       <c r="E37">
-        <v>-3.429999999999996</v>
+        <v>-2.987999999999996</v>
       </c>
       <c r="F37">
-        <v>15.47</v>
+        <v>15.912</v>
       </c>
       <c r="G37">
         <v>7.41</v>
@@ -4321,28 +4321,28 @@
         <v>13.375</v>
       </c>
       <c r="M37">
-        <v>0.7781410000000001</v>
+        <v>0.8003736000000001</v>
       </c>
       <c r="N37">
-        <v>12.596859</v>
+        <v>12.5746264</v>
       </c>
       <c r="O37">
-        <v>3.7790577</v>
+        <v>3.77238792</v>
       </c>
       <c r="P37">
-        <v>8.817801299999999</v>
+        <v>8.80223848</v>
       </c>
       <c r="Q37">
-        <v>11.8178013</v>
+        <v>11.80223848</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1676399204280457</v>
+        <v>0.16912888593607</v>
       </c>
       <c r="T37">
-        <v>0.8495218460715728</v>
+        <v>0.8599035725424196</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.18840158788703</v>
+        <v>16.7109459882235</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1209180869990848</v>
+        <v>0.1205467257199399</v>
       </c>
       <c r="C38">
-        <v>39.0450422923758</v>
+        <v>38.8392684317175</v>
       </c>
       <c r="D38">
-        <v>47.54704229237581</v>
+        <v>47.7832684317175</v>
       </c>
       <c r="E38">
-        <v>-2.987999999999998</v>
+        <v>-2.545999999999999</v>
       </c>
       <c r="F38">
-        <v>15.912</v>
+        <v>16.354</v>
       </c>
       <c r="G38">
         <v>7.41</v>
@@ -4403,28 +4403,28 @@
         <v>13.375</v>
       </c>
       <c r="M38">
-        <v>0.8003736</v>
+        <v>0.8226062</v>
       </c>
       <c r="N38">
-        <v>12.5746264</v>
+        <v>12.5523938</v>
       </c>
       <c r="O38">
-        <v>3.77238792</v>
+        <v>3.76571814</v>
       </c>
       <c r="P38">
-        <v>8.80223848</v>
+        <v>8.78667566</v>
       </c>
       <c r="Q38">
-        <v>11.80223848</v>
+        <v>11.78667566</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.16912888593607</v>
+        <v>0.1706651201903808</v>
       </c>
       <c r="T38">
-        <v>0.8599035725424196</v>
+        <v>0.8706148776313882</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>16.7109459882235</v>
+        <v>16.2592987993526</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1205467257199399</v>
+        <v>0.120175364440795</v>
       </c>
       <c r="C39">
-        <v>38.8392684317175</v>
+        <v>38.63585355758471</v>
       </c>
       <c r="D39">
-        <v>47.7832684317175</v>
+        <v>48.02185355758471</v>
       </c>
       <c r="E39">
-        <v>-2.545999999999999</v>
+        <v>-2.103999999999996</v>
       </c>
       <c r="F39">
-        <v>16.354</v>
+        <v>16.796</v>
       </c>
       <c r="G39">
         <v>7.41</v>
@@ -4485,28 +4485,28 @@
         <v>13.375</v>
       </c>
       <c r="M39">
-        <v>0.8226062</v>
+        <v>0.8448388000000001</v>
       </c>
       <c r="N39">
-        <v>12.5523938</v>
+        <v>12.5301612</v>
       </c>
       <c r="O39">
-        <v>3.76571814</v>
+        <v>3.75904836</v>
       </c>
       <c r="P39">
-        <v>8.78667566</v>
+        <v>8.771112840000001</v>
       </c>
       <c r="Q39">
-        <v>11.78667566</v>
+        <v>11.77111284</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1706651201903808</v>
+        <v>0.172250910388379</v>
       </c>
       <c r="T39">
-        <v>0.8706148776313882</v>
+        <v>0.8816717086909691</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.2592987993526</v>
+        <v>15.8314225151591</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.120175364440795</v>
+        <v>0.1198040031616501</v>
       </c>
       <c r="C40">
-        <v>38.63585355758471</v>
+        <v>38.43483318303956</v>
       </c>
       <c r="D40">
-        <v>48.02185355758471</v>
+        <v>48.26283318303956</v>
       </c>
       <c r="E40">
-        <v>-2.103999999999996</v>
+        <v>-1.661999999999995</v>
       </c>
       <c r="F40">
-        <v>16.796</v>
+        <v>17.238</v>
       </c>
       <c r="G40">
         <v>7.41</v>
@@ -4567,28 +4567,28 @@
         <v>13.375</v>
       </c>
       <c r="M40">
-        <v>0.8448388000000001</v>
+        <v>0.8670714000000002</v>
       </c>
       <c r="N40">
-        <v>12.5301612</v>
+        <v>12.5079286</v>
       </c>
       <c r="O40">
-        <v>3.75904836</v>
+        <v>3.75237858</v>
       </c>
       <c r="P40">
-        <v>8.771112840000001</v>
+        <v>8.755550019999999</v>
       </c>
       <c r="Q40">
-        <v>11.77111284</v>
+        <v>11.75555002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.172250910388379</v>
+        <v>0.1738886937076231</v>
       </c>
       <c r="T40">
-        <v>0.8816717086909691</v>
+        <v>0.8930910588016836</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>15.8314225151591</v>
+        <v>15.425488604514</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1198040031616501</v>
+        <v>0.1194326418825052</v>
       </c>
       <c r="C41">
-        <v>38.43483318303956</v>
+        <v>38.23624353757512</v>
       </c>
       <c r="D41">
-        <v>48.26283318303956</v>
+        <v>48.50624353757512</v>
       </c>
       <c r="E41">
-        <v>-1.661999999999995</v>
+        <v>-1.219999999999995</v>
       </c>
       <c r="F41">
-        <v>17.238</v>
+        <v>17.68</v>
       </c>
       <c r="G41">
         <v>7.41</v>
@@ -4649,28 +4649,28 @@
         <v>13.375</v>
       </c>
       <c r="M41">
-        <v>0.8670714000000002</v>
+        <v>0.8893040000000001</v>
       </c>
       <c r="N41">
-        <v>12.5079286</v>
+        <v>12.485696</v>
       </c>
       <c r="O41">
-        <v>3.75237858</v>
+        <v>3.7457088</v>
       </c>
       <c r="P41">
-        <v>8.755550019999999</v>
+        <v>8.739987200000002</v>
       </c>
       <c r="Q41">
-        <v>11.75555002</v>
+        <v>11.7399872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1738886937076231</v>
+        <v>0.1755810698041753</v>
       </c>
       <c r="T41">
-        <v>0.8930910588016836</v>
+        <v>0.9048910539160887</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.425488604514</v>
+        <v>15.03985138940115</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1194326418825052</v>
+        <v>0.1190612806033603</v>
       </c>
       <c r="C42">
-        <v>38.23624353757512</v>
+        <v>38.04012158527338</v>
       </c>
       <c r="D42">
-        <v>48.50624353757512</v>
+        <v>48.75212158527339</v>
       </c>
       <c r="E42">
-        <v>-1.219999999999995</v>
+        <v>-0.7779999999999951</v>
       </c>
       <c r="F42">
-        <v>17.68</v>
+        <v>18.122</v>
       </c>
       <c r="G42">
         <v>7.41</v>
@@ -4731,28 +4731,28 @@
         <v>13.375</v>
       </c>
       <c r="M42">
-        <v>0.8893040000000001</v>
+        <v>0.9115366000000001</v>
       </c>
       <c r="N42">
-        <v>12.485696</v>
+        <v>12.4634634</v>
       </c>
       <c r="O42">
-        <v>3.7457088</v>
+        <v>3.73903902</v>
       </c>
       <c r="P42">
-        <v>8.739987200000002</v>
+        <v>8.72442438</v>
       </c>
       <c r="Q42">
-        <v>11.7399872</v>
+        <v>11.72442438</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1755810698041753</v>
+        <v>0.1773308145819666</v>
       </c>
       <c r="T42">
-        <v>0.9048910539160887</v>
+        <v>0.9170910488648804</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.03985138940115</v>
+        <v>14.67302574575722</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1190612806033603</v>
+        <v>0.1186899193242154</v>
       </c>
       <c r="C43">
-        <v>38.04012158527338</v>
+        <v>37.84650504351819</v>
       </c>
       <c r="D43">
-        <v>48.75212158527339</v>
+        <v>49.0005050435182</v>
       </c>
       <c r="E43">
-        <v>-0.7779999999999951</v>
+        <v>-0.335999999999995</v>
       </c>
       <c r="F43">
-        <v>18.122</v>
+        <v>18.564</v>
       </c>
       <c r="G43">
         <v>7.41</v>
@@ -4813,28 +4813,28 @@
         <v>13.375</v>
       </c>
       <c r="M43">
-        <v>0.9115366000000001</v>
+        <v>0.9337692000000002</v>
       </c>
       <c r="N43">
-        <v>12.4634634</v>
+        <v>12.4412308</v>
       </c>
       <c r="O43">
-        <v>3.73903902</v>
+        <v>3.73236924</v>
       </c>
       <c r="P43">
-        <v>8.72442438</v>
+        <v>8.708861559999999</v>
       </c>
       <c r="Q43">
-        <v>11.72442438</v>
+        <v>11.70886156</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1773308145819666</v>
+        <v>0.1791408953865782</v>
       </c>
       <c r="T43">
-        <v>0.9170910488648804</v>
+        <v>0.9297117332946648</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>14.67302574575722</v>
+        <v>14.32366798990585</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1186899193242154</v>
+        <v>0.1183185580450705</v>
       </c>
       <c r="C44">
-        <v>37.8465050435182</v>
+        <v>37.65543240228337</v>
       </c>
       <c r="D44">
-        <v>49.0005050435182</v>
+        <v>49.25143240228336</v>
       </c>
       <c r="E44">
-        <v>-0.3359999999999985</v>
+        <v>0.1060000000000016</v>
       </c>
       <c r="F44">
-        <v>18.564</v>
+        <v>19.006</v>
       </c>
       <c r="G44">
         <v>7.41</v>
@@ -4895,28 +4895,28 @@
         <v>13.375</v>
       </c>
       <c r="M44">
-        <v>0.9337692</v>
+        <v>0.9560018</v>
       </c>
       <c r="N44">
-        <v>12.4412308</v>
+        <v>12.4189982</v>
       </c>
       <c r="O44">
-        <v>3.73236924</v>
+        <v>3.72569946</v>
       </c>
       <c r="P44">
-        <v>8.708861559999999</v>
+        <v>8.693298740000001</v>
       </c>
       <c r="Q44">
-        <v>11.70886156</v>
+        <v>11.69329874</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1791408953865782</v>
+        <v>0.1810144877983692</v>
       </c>
       <c r="T44">
-        <v>0.9297117332946646</v>
+        <v>0.9427752487570732</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.32366798990586</v>
+        <v>13.99055943200107</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1183185580450705</v>
+        <v>0.1179471967659256</v>
       </c>
       <c r="C45">
-        <v>37.65543240228337</v>
+        <v>37.46694294401613</v>
       </c>
       <c r="D45">
-        <v>49.25143240228336</v>
+        <v>49.50494294401613</v>
       </c>
       <c r="E45">
-        <v>0.1060000000000016</v>
+        <v>0.5480000000000018</v>
       </c>
       <c r="F45">
-        <v>19.006</v>
+        <v>19.448</v>
       </c>
       <c r="G45">
         <v>7.41</v>
@@ -4977,28 +4977,28 @@
         <v>13.375</v>
       </c>
       <c r="M45">
-        <v>0.9560018</v>
+        <v>0.9782343999999999</v>
       </c>
       <c r="N45">
-        <v>12.4189982</v>
+        <v>12.3967656</v>
       </c>
       <c r="O45">
-        <v>3.72569946</v>
+        <v>3.71902968</v>
       </c>
       <c r="P45">
-        <v>8.693298740000001</v>
+        <v>8.67773592</v>
       </c>
       <c r="Q45">
-        <v>11.69329874</v>
+        <v>11.67773592</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1810144877983692</v>
+        <v>0.1829549942248671</v>
       </c>
       <c r="T45">
-        <v>0.9427752487570732</v>
+        <v>0.956305318343139</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>13.99055943200107</v>
+        <v>13.67259217218286</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1179471967659256</v>
+        <v>0.1175758354867807</v>
       </c>
       <c r="C46">
-        <v>37.46694294401613</v>
+        <v>37.28107676413823</v>
       </c>
       <c r="D46">
-        <v>49.50494294401613</v>
+        <v>49.76107676413823</v>
       </c>
       <c r="E46">
-        <v>0.5480000000000018</v>
+        <v>0.990000000000002</v>
       </c>
       <c r="F46">
-        <v>19.448</v>
+        <v>19.89</v>
       </c>
       <c r="G46">
         <v>7.41</v>
@@ -5059,28 +5059,28 @@
         <v>13.375</v>
       </c>
       <c r="M46">
-        <v>0.9782343999999999</v>
+        <v>1.000467</v>
       </c>
       <c r="N46">
-        <v>12.3967656</v>
+        <v>12.374533</v>
       </c>
       <c r="O46">
-        <v>3.71902968</v>
+        <v>3.7123599</v>
       </c>
       <c r="P46">
-        <v>8.67773592</v>
+        <v>8.6621731</v>
       </c>
       <c r="Q46">
-        <v>11.67773592</v>
+        <v>11.6621731</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1829549942248671</v>
+        <v>0.1849660645214194</v>
       </c>
       <c r="T46">
-        <v>0.956305318343139</v>
+        <v>0.9703273904596075</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>13.67259217218286</v>
+        <v>13.3687567905788</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1175758354867807</v>
+        <v>0.1172044742076357</v>
       </c>
       <c r="C47">
-        <v>37.28107676413823</v>
+        <v>37.0978747921865</v>
       </c>
       <c r="D47">
-        <v>49.76107676413823</v>
+        <v>50.0198747921865</v>
       </c>
       <c r="E47">
-        <v>0.990000000000002</v>
+        <v>1.432000000000002</v>
       </c>
       <c r="F47">
-        <v>19.89</v>
+        <v>20.332</v>
       </c>
       <c r="G47">
         <v>7.41</v>
@@ -5141,28 +5141,28 @@
         <v>13.375</v>
       </c>
       <c r="M47">
-        <v>1.000467</v>
+        <v>1.0226996</v>
       </c>
       <c r="N47">
-        <v>12.374533</v>
+        <v>12.3523004</v>
       </c>
       <c r="O47">
-        <v>3.7123599</v>
+        <v>3.70569012</v>
       </c>
       <c r="P47">
-        <v>8.6621731</v>
+        <v>8.646610280000001</v>
       </c>
       <c r="Q47">
-        <v>11.6621731</v>
+        <v>11.64661028</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1849660645214194</v>
+        <v>0.1870516189030292</v>
       </c>
       <c r="T47">
-        <v>0.9703273904596075</v>
+        <v>0.9848687985803893</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.3687567905788</v>
+        <v>13.07813164295752</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1172044742076357</v>
+        <v>0.1173266129284908</v>
       </c>
       <c r="C48">
-        <v>37.0978747921865</v>
+        <v>36.57046094027439</v>
       </c>
       <c r="D48">
-        <v>50.0198747921865</v>
+        <v>49.93446094027438</v>
       </c>
       <c r="E48">
-        <v>1.432000000000002</v>
+        <v>1.874000000000002</v>
       </c>
       <c r="F48">
-        <v>20.332</v>
+        <v>20.774</v>
       </c>
       <c r="G48">
         <v>7.41</v>
@@ -5223,45 +5223,45 @@
         <v>13.375</v>
       </c>
       <c r="M48">
-        <v>1.0226996</v>
+        <v>1.0760932</v>
       </c>
       <c r="N48">
-        <v>12.3523004</v>
+        <v>12.2989068</v>
       </c>
       <c r="O48">
-        <v>3.70569012</v>
+        <v>3.68967204</v>
       </c>
       <c r="P48">
-        <v>8.646610280000001</v>
+        <v>8.60923476</v>
       </c>
       <c r="Q48">
-        <v>11.64661028</v>
+        <v>11.60923476</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1870516189030292</v>
+        <v>0.1892158734499827</v>
       </c>
       <c r="T48">
-        <v>0.9848687985803893</v>
+        <v>0.9999589390830876</v>
       </c>
       <c r="U48">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y48">
-        <v>13.07813164295752</v>
+        <v>12.42922081470267</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1173266129284908</v>
+        <v>0.1169657516493459</v>
       </c>
       <c r="C49">
-        <v>36.57046094027439</v>
+        <v>36.38166438477819</v>
       </c>
       <c r="D49">
-        <v>49.93446094027438</v>
+        <v>50.1876643847782</v>
       </c>
       <c r="E49">
-        <v>1.874000000000002</v>
+        <v>2.316000000000006</v>
       </c>
       <c r="F49">
-        <v>20.774</v>
+        <v>21.216</v>
       </c>
       <c r="G49">
         <v>7.41</v>
@@ -5305,28 +5305,28 @@
         <v>13.375</v>
       </c>
       <c r="M49">
-        <v>1.0760932</v>
+        <v>1.0989888</v>
       </c>
       <c r="N49">
-        <v>12.2989068</v>
+        <v>12.2760112</v>
       </c>
       <c r="O49">
-        <v>3.68967204</v>
+        <v>3.682803359999999</v>
       </c>
       <c r="P49">
-        <v>8.60923476</v>
+        <v>8.59320784</v>
       </c>
       <c r="Q49">
-        <v>11.60923476</v>
+        <v>11.59320784</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1892158734499827</v>
+        <v>0.1914633685564345</v>
       </c>
       <c r="T49">
-        <v>0.9999589390830876</v>
+        <v>1.01562946960512</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>12.42922081470267</v>
+        <v>12.17027871439636</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1169657516493459</v>
+        <v>0.116604890370201</v>
       </c>
       <c r="C50">
-        <v>36.3816643847782</v>
+        <v>36.19544876171172</v>
       </c>
       <c r="D50">
-        <v>50.1876643847782</v>
+        <v>50.44344876171171</v>
       </c>
       <c r="E50">
-        <v>2.316000000000003</v>
+        <v>2.758000000000003</v>
       </c>
       <c r="F50">
-        <v>21.216</v>
+        <v>21.658</v>
       </c>
       <c r="G50">
         <v>7.41</v>
@@ -5387,28 +5387,28 @@
         <v>13.375</v>
       </c>
       <c r="M50">
-        <v>1.0989888</v>
+        <v>1.1218844</v>
       </c>
       <c r="N50">
-        <v>12.2760112</v>
+        <v>12.2531156</v>
       </c>
       <c r="O50">
-        <v>3.682803359999999</v>
+        <v>3.67593468</v>
       </c>
       <c r="P50">
-        <v>8.59320784</v>
+        <v>8.57718092</v>
       </c>
       <c r="Q50">
-        <v>11.59320784</v>
+        <v>11.57718092</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1914633685564345</v>
+        <v>0.1937990007258844</v>
       </c>
       <c r="T50">
-        <v>1.01562946960512</v>
+        <v>1.03191453073586</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>12.17027871439636</v>
+        <v>11.92190567940868</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.116604890370201</v>
+        <v>0.1162440290910561</v>
       </c>
       <c r="C51">
-        <v>36.19544876171172</v>
+        <v>36.01185373484437</v>
       </c>
       <c r="D51">
-        <v>50.44344876171171</v>
+        <v>50.70185373484438</v>
       </c>
       <c r="E51">
-        <v>2.758000000000003</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="F51">
-        <v>21.658</v>
+        <v>22.1</v>
       </c>
       <c r="G51">
         <v>7.41</v>
@@ -5469,28 +5469,28 @@
         <v>13.375</v>
       </c>
       <c r="M51">
-        <v>1.1218844</v>
+        <v>1.14478</v>
       </c>
       <c r="N51">
-        <v>12.2531156</v>
+        <v>12.23022</v>
       </c>
       <c r="O51">
-        <v>3.67593468</v>
+        <v>3.669065999999999</v>
       </c>
       <c r="P51">
-        <v>8.57718092</v>
+        <v>8.561154</v>
       </c>
       <c r="Q51">
-        <v>11.57718092</v>
+        <v>11.561154</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1937990007258844</v>
+        <v>0.1962280581821123</v>
       </c>
       <c r="T51">
-        <v>1.03191453073586</v>
+        <v>1.04885099431183</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>11.92190567940868</v>
+        <v>11.68346756582051</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1162440290910561</v>
+        <v>0.1158831678119112</v>
       </c>
       <c r="C52">
-        <v>36.01185373484437</v>
+        <v>35.83091978486765</v>
       </c>
       <c r="D52">
-        <v>50.70185373484438</v>
+        <v>50.96291978486764</v>
       </c>
       <c r="E52">
-        <v>3.200000000000003</v>
+        <v>3.642000000000003</v>
       </c>
       <c r="F52">
-        <v>22.1</v>
+        <v>22.542</v>
       </c>
       <c r="G52">
         <v>7.41</v>
@@ -5551,28 +5551,28 @@
         <v>13.375</v>
       </c>
       <c r="M52">
-        <v>1.14478</v>
+        <v>1.1676756</v>
       </c>
       <c r="N52">
-        <v>12.23022</v>
+        <v>12.2073244</v>
       </c>
       <c r="O52">
-        <v>3.669065999999999</v>
+        <v>3.66219732</v>
       </c>
       <c r="P52">
-        <v>8.561154</v>
+        <v>8.54512708</v>
       </c>
       <c r="Q52">
-        <v>11.561154</v>
+        <v>11.54512708</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1962280581821123</v>
+        <v>0.1987562608406352</v>
       </c>
       <c r="T52">
-        <v>1.04885099431183</v>
+        <v>1.06647874211539</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>11.68346756582051</v>
+        <v>11.45437996649069</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1158831678119112</v>
+        <v>0.1155223065327663</v>
       </c>
       <c r="C53">
-        <v>35.83091978486765</v>
+        <v>35.6526882305355</v>
       </c>
       <c r="D53">
-        <v>50.96291978486764</v>
+        <v>51.2266882305355</v>
       </c>
       <c r="E53">
-        <v>3.642000000000003</v>
+        <v>4.084000000000003</v>
       </c>
       <c r="F53">
-        <v>22.542</v>
+        <v>22.984</v>
       </c>
       <c r="G53">
         <v>7.41</v>
@@ -5633,28 +5633,28 @@
         <v>13.375</v>
       </c>
       <c r="M53">
-        <v>1.1676756</v>
+        <v>1.1905712</v>
       </c>
       <c r="N53">
-        <v>12.2073244</v>
+        <v>12.1844288</v>
       </c>
       <c r="O53">
-        <v>3.66219732</v>
+        <v>3.65532864</v>
       </c>
       <c r="P53">
-        <v>8.54512708</v>
+        <v>8.529100159999999</v>
       </c>
       <c r="Q53">
-        <v>11.54512708</v>
+        <v>11.52910016</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1987562608406352</v>
+        <v>0.2013898052765965</v>
       </c>
       <c r="T53">
-        <v>1.06647874211539</v>
+        <v>1.084840979410765</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>11.45437996649069</v>
+        <v>11.23410342867356</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1155223065327663</v>
+        <v>0.1151614452536214</v>
       </c>
       <c r="C54">
-        <v>35.6526882305355</v>
+        <v>35.47720125046517</v>
       </c>
       <c r="D54">
-        <v>51.2266882305355</v>
+        <v>51.49320125046517</v>
       </c>
       <c r="E54">
-        <v>4.084000000000003</v>
+        <v>4.526000000000003</v>
       </c>
       <c r="F54">
-        <v>22.984</v>
+        <v>23.426</v>
       </c>
       <c r="G54">
         <v>7.41</v>
@@ -5715,28 +5715,28 @@
         <v>13.375</v>
       </c>
       <c r="M54">
-        <v>1.1905712</v>
+        <v>1.2134668</v>
       </c>
       <c r="N54">
-        <v>12.1844288</v>
+        <v>12.1615332</v>
       </c>
       <c r="O54">
-        <v>3.65532864</v>
+        <v>3.648459959999999</v>
       </c>
       <c r="P54">
-        <v>8.529100159999999</v>
+        <v>8.513073240000001</v>
       </c>
       <c r="Q54">
-        <v>11.52910016</v>
+        <v>11.51307324</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2013898052765965</v>
+        <v>0.2041354154332371</v>
       </c>
       <c r="T54">
-        <v>1.084840979410765</v>
+        <v>1.103984588505944</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.23410342867356</v>
+        <v>11.02213921303821</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1151614452536214</v>
+        <v>0.1148005839744765</v>
       </c>
       <c r="C55">
-        <v>35.47720125046517</v>
+        <v>35.3045019056217</v>
       </c>
       <c r="D55">
-        <v>51.49320125046517</v>
+        <v>51.7625019056217</v>
       </c>
       <c r="E55">
-        <v>4.526000000000003</v>
+        <v>4.968000000000004</v>
       </c>
       <c r="F55">
-        <v>23.426</v>
+        <v>23.868</v>
       </c>
       <c r="G55">
         <v>7.41</v>
@@ -5797,28 +5797,28 @@
         <v>13.375</v>
       </c>
       <c r="M55">
-        <v>1.2134668</v>
+        <v>1.2363624</v>
       </c>
       <c r="N55">
-        <v>12.1615332</v>
+        <v>12.1386376</v>
       </c>
       <c r="O55">
-        <v>3.648459959999999</v>
+        <v>3.64159128</v>
       </c>
       <c r="P55">
-        <v>8.513073240000001</v>
+        <v>8.497046319999999</v>
       </c>
       <c r="Q55">
-        <v>11.51307324</v>
+        <v>11.49704632</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2041354154332371</v>
+        <v>0.2070003999445142</v>
       </c>
       <c r="T55">
-        <v>1.103984588505944</v>
+        <v>1.123960528431347</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.02213921303821</v>
+        <v>10.81802552390788</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1148005839744765</v>
+        <v>0.1144397226953316</v>
       </c>
       <c r="C56">
-        <v>35.3045019056217</v>
+        <v>35.13463416251196</v>
       </c>
       <c r="D56">
-        <v>51.7625019056217</v>
+        <v>52.03463416251196</v>
       </c>
       <c r="E56">
-        <v>4.968000000000004</v>
+        <v>5.410000000000004</v>
       </c>
       <c r="F56">
-        <v>23.868</v>
+        <v>24.31</v>
       </c>
       <c r="G56">
         <v>7.41</v>
@@ -5879,28 +5879,28 @@
         <v>13.375</v>
       </c>
       <c r="M56">
-        <v>1.2363624</v>
+        <v>1.259258</v>
       </c>
       <c r="N56">
-        <v>12.1386376</v>
+        <v>12.115742</v>
       </c>
       <c r="O56">
-        <v>3.64159128</v>
+        <v>3.6347226</v>
       </c>
       <c r="P56">
-        <v>8.497046319999999</v>
+        <v>8.481019400000001</v>
       </c>
       <c r="Q56">
-        <v>11.49704632</v>
+        <v>11.4810194</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2070003999445142</v>
+        <v>0.2099927171007369</v>
       </c>
       <c r="T56">
-        <v>1.123960528431347</v>
+        <v>1.144824287908991</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>10.81802552390788</v>
+        <v>10.62133415074592</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1144397226953316</v>
+        <v>0.1140788614161867</v>
       </c>
       <c r="C57">
-        <v>35.13463416251196</v>
+        <v>34.96764291711414</v>
       </c>
       <c r="D57">
-        <v>52.03463416251196</v>
+        <v>52.30964291711415</v>
       </c>
       <c r="E57">
-        <v>5.410000000000004</v>
+        <v>5.852000000000004</v>
       </c>
       <c r="F57">
-        <v>24.31</v>
+        <v>24.752</v>
       </c>
       <c r="G57">
         <v>7.41</v>
@@ -5961,28 +5961,28 @@
         <v>13.375</v>
       </c>
       <c r="M57">
-        <v>1.259258</v>
+        <v>1.2821536</v>
       </c>
       <c r="N57">
-        <v>12.115742</v>
+        <v>12.0928464</v>
       </c>
       <c r="O57">
-        <v>3.6347226</v>
+        <v>3.62785392</v>
       </c>
       <c r="P57">
-        <v>8.481019400000001</v>
+        <v>8.464992479999999</v>
       </c>
       <c r="Q57">
-        <v>11.4810194</v>
+        <v>11.46499248</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2099927171007369</v>
+        <v>0.2131210486731517</v>
       </c>
       <c r="T57">
-        <v>1.144824287908991</v>
+        <v>1.166636400090164</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.62133415074592</v>
+        <v>10.43166746948259</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1140788614161867</v>
+        <v>0.1137180001370418</v>
       </c>
       <c r="C58">
-        <v>34.96764291711414</v>
+        <v>34.80357401956999</v>
       </c>
       <c r="D58">
-        <v>52.30964291711415</v>
+        <v>52.58757401956999</v>
       </c>
       <c r="E58">
-        <v>5.852000000000004</v>
+        <v>6.294000000000004</v>
       </c>
       <c r="F58">
-        <v>24.752</v>
+        <v>25.194</v>
       </c>
       <c r="G58">
         <v>7.41</v>
@@ -6043,28 +6043,28 @@
         <v>13.375</v>
       </c>
       <c r="M58">
-        <v>1.2821536</v>
+        <v>1.3050492</v>
       </c>
       <c r="N58">
-        <v>12.0928464</v>
+        <v>12.0699508</v>
       </c>
       <c r="O58">
-        <v>3.62785392</v>
+        <v>3.62098524</v>
       </c>
       <c r="P58">
-        <v>8.464992479999999</v>
+        <v>8.448965560000001</v>
       </c>
       <c r="Q58">
-        <v>11.46499248</v>
+        <v>11.44896556</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2131210486731517</v>
+        <v>0.2163948840396321</v>
       </c>
       <c r="T58">
-        <v>1.166636400090164</v>
+        <v>1.189463029116973</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>10.43166746948259</v>
+        <v>10.24865575949167</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1137180001370418</v>
+        <v>0.1133571388578969</v>
       </c>
       <c r="C59">
-        <v>34.80357401956999</v>
+        <v>34.64247429966836</v>
       </c>
       <c r="D59">
-        <v>52.58757401956999</v>
+        <v>52.86847429966838</v>
       </c>
       <c r="E59">
-        <v>6.294000000000004</v>
+        <v>6.736000000000008</v>
       </c>
       <c r="F59">
-        <v>25.194</v>
+        <v>25.63600000000001</v>
       </c>
       <c r="G59">
         <v>7.41</v>
@@ -6125,28 +6125,28 @@
         <v>13.375</v>
       </c>
       <c r="M59">
-        <v>1.3050492</v>
+        <v>1.3279448</v>
       </c>
       <c r="N59">
-        <v>12.0699508</v>
+        <v>12.0470552</v>
       </c>
       <c r="O59">
-        <v>3.62098524</v>
+        <v>3.614116559999999</v>
       </c>
       <c r="P59">
-        <v>8.448965560000001</v>
+        <v>8.43293864</v>
       </c>
       <c r="Q59">
-        <v>11.44896556</v>
+        <v>11.43293864</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2163948840396321</v>
+        <v>0.219824616328326</v>
       </c>
       <c r="T59">
-        <v>1.189463029116973</v>
+        <v>1.213376640478392</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.24865575949167</v>
+        <v>10.07195479812112</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1133571388578969</v>
+        <v>0.112996277578752</v>
       </c>
       <c r="C60">
-        <v>34.64247429966836</v>
+        <v>34.48439159315029</v>
       </c>
       <c r="D60">
-        <v>52.86847429966836</v>
+        <v>53.15239159315029</v>
       </c>
       <c r="E60">
-        <v>6.736000000000001</v>
+        <v>7.178000000000001</v>
       </c>
       <c r="F60">
-        <v>25.636</v>
+        <v>26.078</v>
       </c>
       <c r="G60">
         <v>7.41</v>
@@ -6207,28 +6207,28 @@
         <v>13.375</v>
       </c>
       <c r="M60">
-        <v>1.3279448</v>
+        <v>1.3508404</v>
       </c>
       <c r="N60">
-        <v>12.0470552</v>
+        <v>12.0241596</v>
       </c>
       <c r="O60">
-        <v>3.614116559999999</v>
+        <v>3.60724788</v>
       </c>
       <c r="P60">
-        <v>8.43293864</v>
+        <v>8.416911720000002</v>
       </c>
       <c r="Q60">
-        <v>11.43293864</v>
+        <v>11.41691172</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.219824616328326</v>
+        <v>0.2234216526311024</v>
       </c>
       <c r="T60">
-        <v>1.213376640478391</v>
+        <v>1.238456769467196</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.07195479812113</v>
+        <v>9.901243699847889</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.112996277578752</v>
+        <v>0.1133494162996071</v>
       </c>
       <c r="C61">
-        <v>34.48439159315029</v>
+        <v>33.76451846550782</v>
       </c>
       <c r="D61">
-        <v>53.15239159315029</v>
+        <v>52.87451846550782</v>
       </c>
       <c r="E61">
-        <v>7.178000000000001</v>
+        <v>7.620000000000001</v>
       </c>
       <c r="F61">
-        <v>26.078</v>
+        <v>26.52</v>
       </c>
       <c r="G61">
         <v>7.41</v>
@@ -6289,45 +6289,45 @@
         <v>13.375</v>
       </c>
       <c r="M61">
-        <v>1.3508404</v>
+        <v>1.41882</v>
       </c>
       <c r="N61">
-        <v>12.0241596</v>
+        <v>11.95618</v>
       </c>
       <c r="O61">
-        <v>3.60724788</v>
+        <v>3.586854</v>
       </c>
       <c r="P61">
-        <v>8.416911720000002</v>
+        <v>8.369326000000001</v>
       </c>
       <c r="Q61">
-        <v>11.41691172</v>
+        <v>11.369326</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2234216526311024</v>
+        <v>0.2271985407490177</v>
       </c>
       <c r="T61">
-        <v>1.238456769467196</v>
+        <v>1.264790904905442</v>
       </c>
       <c r="U61">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>9.901243699847889</v>
+        <v>9.42684766214178</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1133494162996071</v>
+        <v>0.1130004550204622</v>
       </c>
       <c r="C62">
-        <v>33.76451846550782</v>
+        <v>33.59708743371311</v>
       </c>
       <c r="D62">
-        <v>52.87451846550782</v>
+        <v>53.14908743371312</v>
       </c>
       <c r="E62">
-        <v>7.620000000000001</v>
+        <v>8.062000000000001</v>
       </c>
       <c r="F62">
-        <v>26.52</v>
+        <v>26.962</v>
       </c>
       <c r="G62">
         <v>7.41</v>
@@ -6371,28 +6371,28 @@
         <v>13.375</v>
       </c>
       <c r="M62">
-        <v>1.41882</v>
+        <v>1.442467</v>
       </c>
       <c r="N62">
-        <v>11.95618</v>
+        <v>11.932533</v>
       </c>
       <c r="O62">
-        <v>3.586854</v>
+        <v>3.5797599</v>
       </c>
       <c r="P62">
-        <v>8.369326000000001</v>
+        <v>8.3527731</v>
       </c>
       <c r="Q62">
-        <v>11.369326</v>
+        <v>11.3527731</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2271985407490177</v>
+        <v>0.2311691154370825</v>
       </c>
       <c r="T62">
-        <v>1.264790904905442</v>
+        <v>1.2924755088277</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>9.42684766214178</v>
+        <v>9.27230917587716</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1130004550204622</v>
+        <v>0.1126514937413173</v>
       </c>
       <c r="C63">
-        <v>33.59708743371311</v>
+        <v>33.43252287304706</v>
       </c>
       <c r="D63">
-        <v>53.14908743371312</v>
+        <v>53.42652287304706</v>
       </c>
       <c r="E63">
-        <v>8.062000000000001</v>
+        <v>8.504000000000001</v>
       </c>
       <c r="F63">
-        <v>26.962</v>
+        <v>27.404</v>
       </c>
       <c r="G63">
         <v>7.41</v>
@@ -6453,28 +6453,28 @@
         <v>13.375</v>
       </c>
       <c r="M63">
-        <v>1.442467</v>
+        <v>1.466114</v>
       </c>
       <c r="N63">
-        <v>11.932533</v>
+        <v>11.908886</v>
       </c>
       <c r="O63">
-        <v>3.5797599</v>
+        <v>3.5726658</v>
       </c>
       <c r="P63">
-        <v>8.3527731</v>
+        <v>8.3362202</v>
       </c>
       <c r="Q63">
-        <v>11.3527731</v>
+        <v>11.3362202</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2311691154370825</v>
+        <v>0.2353486677403086</v>
       </c>
       <c r="T63">
-        <v>1.2924755088277</v>
+        <v>1.321617197166919</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>9.27230917587716</v>
+        <v>9.122755802072691</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1126514937413173</v>
+        <v>0.1123025324621724</v>
       </c>
       <c r="C64">
-        <v>33.43252287304706</v>
+        <v>33.27086990754002</v>
       </c>
       <c r="D64">
-        <v>53.42652287304706</v>
+        <v>53.70686990754002</v>
       </c>
       <c r="E64">
-        <v>8.504000000000001</v>
+        <v>8.946000000000005</v>
       </c>
       <c r="F64">
-        <v>27.404</v>
+        <v>27.846</v>
       </c>
       <c r="G64">
         <v>7.41</v>
@@ -6535,28 +6535,28 @@
         <v>13.375</v>
       </c>
       <c r="M64">
-        <v>1.466114</v>
+        <v>1.489761</v>
       </c>
       <c r="N64">
-        <v>11.908886</v>
+        <v>11.885239</v>
       </c>
       <c r="O64">
-        <v>3.5726658</v>
+        <v>3.5655717</v>
       </c>
       <c r="P64">
-        <v>8.3362202</v>
+        <v>8.319667300000001</v>
       </c>
       <c r="Q64">
-        <v>11.3362202</v>
+        <v>11.3196673</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2353486677403086</v>
+        <v>0.2397541417896551</v>
       </c>
       <c r="T64">
-        <v>1.321617197166919</v>
+        <v>1.352334111902852</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.122755802072691</v>
+        <v>8.977950154420743</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1123025324621724</v>
+        <v>0.1119535711830275</v>
       </c>
       <c r="C65">
-        <v>33.27086990754002</v>
+        <v>33.11217461334271</v>
       </c>
       <c r="D65">
-        <v>53.70686990754002</v>
+        <v>53.99017461334271</v>
       </c>
       <c r="E65">
-        <v>8.946000000000005</v>
+        <v>9.388000000000005</v>
       </c>
       <c r="F65">
-        <v>27.846</v>
+        <v>28.288</v>
       </c>
       <c r="G65">
         <v>7.41</v>
@@ -6617,28 +6617,28 @@
         <v>13.375</v>
       </c>
       <c r="M65">
-        <v>1.489761</v>
+        <v>1.513408</v>
       </c>
       <c r="N65">
-        <v>11.885239</v>
+        <v>11.861592</v>
       </c>
       <c r="O65">
-        <v>3.5655717</v>
+        <v>3.5584776</v>
       </c>
       <c r="P65">
-        <v>8.319667300000001</v>
+        <v>8.3031144</v>
       </c>
       <c r="Q65">
-        <v>11.3196673</v>
+        <v>11.3031144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2397541417896551</v>
+        <v>0.2444043643972986</v>
       </c>
       <c r="T65">
-        <v>1.352334111902852</v>
+        <v>1.384757521901893</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>8.977950154420743</v>
+        <v>8.837669683257918</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1119535711830275</v>
+        <v>0.1116046099038826</v>
       </c>
       <c r="C66">
-        <v>33.11217461334271</v>
+        <v>32.95648404397149</v>
       </c>
       <c r="D66">
-        <v>53.99017461334271</v>
+        <v>54.27648404397149</v>
       </c>
       <c r="E66">
-        <v>9.388000000000005</v>
+        <v>9.830000000000005</v>
       </c>
       <c r="F66">
-        <v>28.288</v>
+        <v>28.73</v>
       </c>
       <c r="G66">
         <v>7.41</v>
@@ -6699,28 +6699,28 @@
         <v>13.375</v>
       </c>
       <c r="M66">
-        <v>1.513408</v>
+        <v>1.537055</v>
       </c>
       <c r="N66">
-        <v>11.861592</v>
+        <v>11.837945</v>
       </c>
       <c r="O66">
-        <v>3.5584776</v>
+        <v>3.5513835</v>
       </c>
       <c r="P66">
-        <v>8.3031144</v>
+        <v>8.286561499999999</v>
       </c>
       <c r="Q66">
-        <v>11.3031144</v>
+        <v>11.2865615</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2444043643972986</v>
+        <v>0.2493203140110931</v>
       </c>
       <c r="T66">
-        <v>1.384757521901893</v>
+        <v>1.419033698186593</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>8.837669683257918</v>
+        <v>8.701705534284718</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1116046099038826</v>
+        <v>0.1112556486247377</v>
       </c>
       <c r="C67">
-        <v>32.95648404397149</v>
+        <v>32.8038462563614</v>
       </c>
       <c r="D67">
-        <v>54.27648404397149</v>
+        <v>54.56584625636141</v>
       </c>
       <c r="E67">
-        <v>9.830000000000005</v>
+        <v>10.27200000000001</v>
       </c>
       <c r="F67">
-        <v>28.73</v>
+        <v>29.172</v>
       </c>
       <c r="G67">
         <v>7.41</v>
@@ -6781,28 +6781,28 @@
         <v>13.375</v>
       </c>
       <c r="M67">
-        <v>1.537055</v>
+        <v>1.560702</v>
       </c>
       <c r="N67">
-        <v>11.837945</v>
+        <v>11.814298</v>
       </c>
       <c r="O67">
-        <v>3.5513835</v>
+        <v>3.5442894</v>
       </c>
       <c r="P67">
-        <v>8.286561499999999</v>
+        <v>8.270008599999999</v>
       </c>
       <c r="Q67">
-        <v>11.2865615</v>
+        <v>11.2700086</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2493203140110931</v>
+        <v>0.2545254371315814</v>
       </c>
       <c r="T67">
-        <v>1.419033698186593</v>
+        <v>1.4553261201351</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.701705534284718</v>
+        <v>8.569861511037979</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1112556486247377</v>
+        <v>0.1109066873455928</v>
       </c>
       <c r="C68">
-        <v>32.8038462563614</v>
+        <v>32.6543103377571</v>
       </c>
       <c r="D68">
-        <v>54.56584625636141</v>
+        <v>54.8583103377571</v>
       </c>
       <c r="E68">
-        <v>10.27200000000001</v>
+        <v>10.71400000000001</v>
       </c>
       <c r="F68">
-        <v>29.172</v>
+        <v>29.614</v>
       </c>
       <c r="G68">
         <v>7.41</v>
@@ -6863,28 +6863,28 @@
         <v>13.375</v>
       </c>
       <c r="M68">
-        <v>1.560702</v>
+        <v>1.584349</v>
       </c>
       <c r="N68">
-        <v>11.814298</v>
+        <v>11.790651</v>
       </c>
       <c r="O68">
-        <v>3.5442894</v>
+        <v>3.5371953</v>
       </c>
       <c r="P68">
-        <v>8.270008599999999</v>
+        <v>8.2534557</v>
       </c>
       <c r="Q68">
-        <v>11.2700086</v>
+        <v>11.2534557</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2545254371315814</v>
+        <v>0.260046022259372</v>
       </c>
       <c r="T68">
-        <v>1.4553261201351</v>
+        <v>1.493818082807758</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.569861511037979</v>
+        <v>8.44195313027622</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1109066873455928</v>
+        <v>0.1105577260664479</v>
       </c>
       <c r="C69">
-        <v>32.6543103377571</v>
+        <v>32.50792643347281</v>
       </c>
       <c r="D69">
-        <v>54.8583103377571</v>
+        <v>55.15392643347282</v>
       </c>
       <c r="E69">
-        <v>10.71400000000001</v>
+        <v>11.15600000000001</v>
       </c>
       <c r="F69">
-        <v>29.614</v>
+        <v>30.056</v>
       </c>
       <c r="G69">
         <v>7.41</v>
@@ -6945,28 +6945,28 @@
         <v>13.375</v>
       </c>
       <c r="M69">
-        <v>1.584349</v>
+        <v>1.607996</v>
       </c>
       <c r="N69">
-        <v>11.790651</v>
+        <v>11.767004</v>
       </c>
       <c r="O69">
-        <v>3.5371953</v>
+        <v>3.5301012</v>
       </c>
       <c r="P69">
-        <v>8.2534557</v>
+        <v>8.236902799999999</v>
       </c>
       <c r="Q69">
-        <v>11.2534557</v>
+        <v>11.2369028</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.260046022259372</v>
+        <v>0.2659116439576496</v>
       </c>
       <c r="T69">
-        <v>1.493818082807758</v>
+        <v>1.534715793147457</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.44195313027622</v>
+        <v>8.317806760713335</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1105577260664479</v>
+        <v>0.110208764787303</v>
       </c>
       <c r="C70">
-        <v>32.50792643347281</v>
+        <v>32.36474577555532</v>
       </c>
       <c r="D70">
-        <v>55.15392643347282</v>
+        <v>55.45274577555532</v>
       </c>
       <c r="E70">
-        <v>11.15600000000001</v>
+        <v>11.59800000000001</v>
       </c>
       <c r="F70">
-        <v>30.056</v>
+        <v>30.498</v>
       </c>
       <c r="G70">
         <v>7.41</v>
@@ -7027,28 +7027,28 @@
         <v>13.375</v>
       </c>
       <c r="M70">
-        <v>1.607996</v>
+        <v>1.631643</v>
       </c>
       <c r="N70">
-        <v>11.767004</v>
+        <v>11.743357</v>
       </c>
       <c r="O70">
-        <v>3.5301012</v>
+        <v>3.5230071</v>
       </c>
       <c r="P70">
-        <v>8.236902799999999</v>
+        <v>8.2203499</v>
       </c>
       <c r="Q70">
-        <v>11.2369028</v>
+        <v>11.2203499</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2659116439576496</v>
+        <v>0.2721556928622677</v>
       </c>
       <c r="T70">
-        <v>1.534715793147457</v>
+        <v>1.578252065444557</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.317806760713335</v>
+        <v>8.197258836645025</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.110208764787303</v>
+        <v>0.109859803508158</v>
       </c>
       <c r="C71">
-        <v>32.36474577555532</v>
+        <v>32.22482071238323</v>
       </c>
       <c r="D71">
-        <v>55.45274577555532</v>
+        <v>55.75482071238324</v>
       </c>
       <c r="E71">
-        <v>11.59800000000001</v>
+        <v>12.04000000000001</v>
       </c>
       <c r="F71">
-        <v>30.498</v>
+        <v>30.94</v>
       </c>
       <c r="G71">
         <v>7.41</v>
@@ -7109,28 +7109,28 @@
         <v>13.375</v>
       </c>
       <c r="M71">
-        <v>1.631643</v>
+        <v>1.65529</v>
       </c>
       <c r="N71">
-        <v>11.743357</v>
+        <v>11.71971</v>
       </c>
       <c r="O71">
-        <v>3.5230071</v>
+        <v>3.515913</v>
       </c>
       <c r="P71">
-        <v>8.2203499</v>
+        <v>8.203797</v>
       </c>
       <c r="Q71">
-        <v>11.2203499</v>
+        <v>11.203797</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2721556928622677</v>
+        <v>0.2788160116938602</v>
       </c>
       <c r="T71">
-        <v>1.578252065444557</v>
+        <v>1.624690755894796</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.197258836645025</v>
+        <v>8.080155138978668</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.109859803508158</v>
+        <v>0.1095108422290131</v>
       </c>
       <c r="C72">
-        <v>32.22482071238323</v>
+        <v>32.0882047392393</v>
       </c>
       <c r="D72">
-        <v>55.75482071238324</v>
+        <v>56.06020473923931</v>
       </c>
       <c r="E72">
-        <v>12.04000000000001</v>
+        <v>12.48200000000001</v>
       </c>
       <c r="F72">
-        <v>30.94</v>
+        <v>31.38200000000001</v>
       </c>
       <c r="G72">
         <v>7.41</v>
@@ -7191,28 +7191,28 @@
         <v>13.375</v>
       </c>
       <c r="M72">
-        <v>1.65529</v>
+        <v>1.678937</v>
       </c>
       <c r="N72">
-        <v>11.71971</v>
+        <v>11.696063</v>
       </c>
       <c r="O72">
-        <v>3.515913</v>
+        <v>3.5088189</v>
       </c>
       <c r="P72">
-        <v>8.203797</v>
+        <v>8.187244100000001</v>
       </c>
       <c r="Q72">
-        <v>11.203797</v>
+        <v>11.1872441</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2788160116938602</v>
+        <v>0.2859356628586661</v>
       </c>
       <c r="T72">
-        <v>1.624690755894796</v>
+        <v>1.674332114651948</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.080155138978668</v>
+        <v>7.966350137021222</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1095108422290131</v>
+        <v>0.1091618809498683</v>
       </c>
       <c r="C73">
-        <v>32.0882047392393</v>
+        <v>31.95495252989293</v>
       </c>
       <c r="D73">
-        <v>56.06020473923931</v>
+        <v>56.36895252989293</v>
       </c>
       <c r="E73">
-        <v>12.482</v>
+        <v>12.924</v>
       </c>
       <c r="F73">
-        <v>31.382</v>
+        <v>31.824</v>
       </c>
       <c r="G73">
         <v>7.41</v>
@@ -7273,28 +7273,28 @@
         <v>13.375</v>
       </c>
       <c r="M73">
-        <v>1.678937</v>
+        <v>1.702584</v>
       </c>
       <c r="N73">
-        <v>11.696063</v>
+        <v>11.672416</v>
       </c>
       <c r="O73">
-        <v>3.5088189</v>
+        <v>3.5017248</v>
       </c>
       <c r="P73">
-        <v>8.187244100000001</v>
+        <v>8.1706912</v>
       </c>
       <c r="Q73">
-        <v>11.1872441</v>
+        <v>11.1706912</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.285935662858666</v>
+        <v>0.2935638605352437</v>
       </c>
       <c r="T73">
-        <v>1.674332114651948</v>
+        <v>1.727519284748896</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>7.966350137021222</v>
+        <v>7.855706385118149</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1091618809498683</v>
+        <v>0.1088129196707234</v>
       </c>
       <c r="C74">
-        <v>31.95495252989293</v>
+        <v>31.82511996923201</v>
       </c>
       <c r="D74">
-        <v>56.36895252989293</v>
+        <v>56.68111996923201</v>
       </c>
       <c r="E74">
-        <v>12.924</v>
+        <v>13.366</v>
       </c>
       <c r="F74">
-        <v>31.824</v>
+        <v>32.266</v>
       </c>
       <c r="G74">
         <v>7.41</v>
@@ -7355,28 +7355,28 @@
         <v>13.375</v>
       </c>
       <c r="M74">
-        <v>1.702584</v>
+        <v>1.726231</v>
       </c>
       <c r="N74">
-        <v>11.672416</v>
+        <v>11.648769</v>
       </c>
       <c r="O74">
-        <v>3.5017248</v>
+        <v>3.4946307</v>
       </c>
       <c r="P74">
-        <v>8.1706912</v>
+        <v>8.1541383</v>
       </c>
       <c r="Q74">
-        <v>11.1706912</v>
+        <v>11.1541383</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2935638605352437</v>
+        <v>0.301757109891568</v>
       </c>
       <c r="T74">
-        <v>1.727519284748896</v>
+        <v>1.784646245223397</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>7.855706385118149</v>
+        <v>7.748093968883655</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1088129196707234</v>
+        <v>0.1084639583915784</v>
       </c>
       <c r="C75">
-        <v>31.82511996923201</v>
+        <v>31.69876418698523</v>
       </c>
       <c r="D75">
-        <v>56.68111996923201</v>
+        <v>56.99676418698523</v>
       </c>
       <c r="E75">
-        <v>13.366</v>
+        <v>13.808</v>
       </c>
       <c r="F75">
-        <v>32.266</v>
+        <v>32.708</v>
       </c>
       <c r="G75">
         <v>7.41</v>
@@ -7437,28 +7437,28 @@
         <v>13.375</v>
       </c>
       <c r="M75">
-        <v>1.726231</v>
+        <v>1.749878</v>
       </c>
       <c r="N75">
-        <v>11.648769</v>
+        <v>11.625122</v>
       </c>
       <c r="O75">
-        <v>3.4946307</v>
+        <v>3.4875366</v>
       </c>
       <c r="P75">
-        <v>8.1541383</v>
+        <v>8.137585400000001</v>
       </c>
       <c r="Q75">
-        <v>11.1541383</v>
+        <v>11.1375854</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.301757109891568</v>
+        <v>0.3105806091983786</v>
       </c>
       <c r="T75">
-        <v>1.784646245223397</v>
+        <v>1.846167587272859</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.748093968883655</v>
+        <v>7.643389996331174</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1084639583915784</v>
+        <v>0.1085349971124335</v>
       </c>
       <c r="C76">
-        <v>31.69876418698523</v>
+        <v>31.19222322249827</v>
       </c>
       <c r="D76">
-        <v>56.99676418698523</v>
+        <v>56.93222322249828</v>
       </c>
       <c r="E76">
-        <v>13.808</v>
+        <v>14.25000000000001</v>
       </c>
       <c r="F76">
-        <v>32.708</v>
+        <v>33.15000000000001</v>
       </c>
       <c r="G76">
         <v>7.41</v>
@@ -7519,45 +7519,45 @@
         <v>13.375</v>
       </c>
       <c r="M76">
-        <v>1.749878</v>
+        <v>1.800045</v>
       </c>
       <c r="N76">
-        <v>11.625122</v>
+        <v>11.574955</v>
       </c>
       <c r="O76">
-        <v>3.4875366</v>
+        <v>3.4724865</v>
       </c>
       <c r="P76">
-        <v>8.137585400000001</v>
+        <v>8.102468500000001</v>
       </c>
       <c r="Q76">
-        <v>11.1375854</v>
+        <v>11.1024685</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3105806091983786</v>
+        <v>0.3201099884497341</v>
       </c>
       <c r="T76">
-        <v>1.846167587272859</v>
+        <v>1.912610636686278</v>
       </c>
       <c r="U76">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V76">
         <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y76">
-        <v>7.643389996331174</v>
+        <v>7.430369796310647</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1085349971124335</v>
+        <v>0.1081916358332886</v>
       </c>
       <c r="C77">
-        <v>31.19222322249827</v>
+        <v>31.06353959462343</v>
       </c>
       <c r="D77">
-        <v>56.93222322249828</v>
+        <v>57.24553959462344</v>
       </c>
       <c r="E77">
-        <v>14.25000000000001</v>
+        <v>14.69200000000001</v>
       </c>
       <c r="F77">
-        <v>33.15000000000001</v>
+        <v>33.59200000000001</v>
       </c>
       <c r="G77">
         <v>7.41</v>
@@ -7601,28 +7601,28 @@
         <v>13.375</v>
       </c>
       <c r="M77">
-        <v>1.800045</v>
+        <v>1.8240456</v>
       </c>
       <c r="N77">
-        <v>11.574955</v>
+        <v>11.5509544</v>
       </c>
       <c r="O77">
-        <v>3.4724865</v>
+        <v>3.46528632</v>
       </c>
       <c r="P77">
-        <v>8.102468500000001</v>
+        <v>8.08566808</v>
       </c>
       <c r="Q77">
-        <v>11.1024685</v>
+        <v>11.08566808</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3201099884497341</v>
+        <v>0.3304334826387026</v>
       </c>
       <c r="T77">
-        <v>1.912610636686278</v>
+        <v>1.984590606884149</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.430369796310647</v>
+        <v>7.33260177267498</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1081916358332886</v>
+        <v>0.1078482745541437</v>
       </c>
       <c r="C78">
-        <v>31.06353959462343</v>
+        <v>30.93832361225793</v>
       </c>
       <c r="D78">
-        <v>57.24553959462344</v>
+        <v>57.56232361225793</v>
       </c>
       <c r="E78">
-        <v>14.69200000000001</v>
+        <v>15.13400000000001</v>
       </c>
       <c r="F78">
-        <v>33.59200000000001</v>
+        <v>34.03400000000001</v>
       </c>
       <c r="G78">
         <v>7.41</v>
@@ -7683,28 +7683,28 @@
         <v>13.375</v>
       </c>
       <c r="M78">
-        <v>1.8240456</v>
+        <v>1.8480462</v>
       </c>
       <c r="N78">
-        <v>11.5509544</v>
+        <v>11.5269538</v>
       </c>
       <c r="O78">
-        <v>3.46528632</v>
+        <v>3.45808614</v>
       </c>
       <c r="P78">
-        <v>8.08566808</v>
+        <v>8.068867659999999</v>
       </c>
       <c r="Q78">
-        <v>11.08566808</v>
+        <v>11.06886766</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3304334826387026</v>
+        <v>0.341654671974538</v>
       </c>
       <c r="T78">
-        <v>1.984590606884149</v>
+        <v>2.062829704925313</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.33260177267498</v>
+        <v>7.237373178224655</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1078482745541437</v>
+        <v>0.1075049132749988</v>
       </c>
       <c r="C79">
-        <v>30.93832361225793</v>
+        <v>30.8166331632652</v>
       </c>
       <c r="D79">
-        <v>57.56232361225793</v>
+        <v>57.8826331632652</v>
       </c>
       <c r="E79">
-        <v>15.13400000000001</v>
+        <v>15.57600000000001</v>
       </c>
       <c r="F79">
-        <v>34.03400000000001</v>
+        <v>34.47600000000001</v>
       </c>
       <c r="G79">
         <v>7.41</v>
@@ -7765,28 +7765,28 @@
         <v>13.375</v>
       </c>
       <c r="M79">
-        <v>1.8480462</v>
+        <v>1.8720468</v>
       </c>
       <c r="N79">
-        <v>11.5269538</v>
+        <v>11.5029532</v>
       </c>
       <c r="O79">
-        <v>3.45808614</v>
+        <v>3.45088596</v>
       </c>
       <c r="P79">
-        <v>8.068867659999999</v>
+        <v>8.05206724</v>
       </c>
       <c r="Q79">
-        <v>11.06886766</v>
+        <v>11.05206724</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.341654671974538</v>
+        <v>0.3538959694318128</v>
       </c>
       <c r="T79">
-        <v>2.062829704925313</v>
+        <v>2.148181448242946</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.237373178224655</v>
+        <v>7.144586342606392</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1075049132749988</v>
+        <v>0.1071615519958539</v>
       </c>
       <c r="C80">
-        <v>30.8166331632652</v>
+        <v>30.69852743120283</v>
       </c>
       <c r="D80">
-        <v>57.8826331632652</v>
+        <v>58.20652743120284</v>
       </c>
       <c r="E80">
-        <v>15.57600000000001</v>
+        <v>16.01800000000001</v>
       </c>
       <c r="F80">
-        <v>34.47600000000001</v>
+        <v>34.91800000000001</v>
       </c>
       <c r="G80">
         <v>7.41</v>
@@ -7847,28 +7847,28 @@
         <v>13.375</v>
       </c>
       <c r="M80">
-        <v>1.8720468</v>
+        <v>1.8960474</v>
       </c>
       <c r="N80">
-        <v>11.5029532</v>
+        <v>11.4789526</v>
       </c>
       <c r="O80">
-        <v>3.45088596</v>
+        <v>3.44368578</v>
       </c>
       <c r="P80">
-        <v>8.05206724</v>
+        <v>8.03526682</v>
       </c>
       <c r="Q80">
-        <v>11.05206724</v>
+        <v>11.03526682</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3538959694318128</v>
+        <v>0.3673031047421616</v>
       </c>
       <c r="T80">
-        <v>2.148181448242946</v>
+        <v>2.241661929019402</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.144586342606392</v>
+        <v>7.054148540801247</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1071615519958539</v>
+        <v>0.106818190716709</v>
       </c>
       <c r="C81">
-        <v>30.69852743120283</v>
+        <v>30.58406693177816</v>
       </c>
       <c r="D81">
-        <v>58.20652743120284</v>
+        <v>58.53406693177817</v>
       </c>
       <c r="E81">
-        <v>16.01800000000001</v>
+        <v>16.46000000000001</v>
       </c>
       <c r="F81">
-        <v>34.91800000000001</v>
+        <v>35.36000000000001</v>
       </c>
       <c r="G81">
         <v>7.41</v>
@@ -7929,28 +7929,28 @@
         <v>13.375</v>
       </c>
       <c r="M81">
-        <v>1.8960474</v>
+        <v>1.920048</v>
       </c>
       <c r="N81">
-        <v>11.4789526</v>
+        <v>11.454952</v>
       </c>
       <c r="O81">
-        <v>3.44368578</v>
+        <v>3.4364856</v>
       </c>
       <c r="P81">
-        <v>8.03526682</v>
+        <v>8.018466399999999</v>
       </c>
       <c r="Q81">
-        <v>11.03526682</v>
+        <v>11.0184664</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3673031047421616</v>
+        <v>0.3820509535835451</v>
       </c>
       <c r="T81">
-        <v>2.241661929019402</v>
+        <v>2.344490457873503</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.054148540801247</v>
+        <v>6.96597168404123</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.106818190716709</v>
+        <v>0.1064748294375641</v>
       </c>
       <c r="C82">
-        <v>30.58406693177816</v>
+        <v>30.4733135505417</v>
       </c>
       <c r="D82">
-        <v>58.53406693177817</v>
+        <v>58.86531355054171</v>
       </c>
       <c r="E82">
-        <v>16.46000000000001</v>
+        <v>16.90200000000001</v>
       </c>
       <c r="F82">
-        <v>35.36000000000001</v>
+        <v>35.80200000000001</v>
       </c>
       <c r="G82">
         <v>7.41</v>
@@ -8011,28 +8011,28 @@
         <v>13.375</v>
       </c>
       <c r="M82">
-        <v>1.920048</v>
+        <v>1.9440486</v>
       </c>
       <c r="N82">
-        <v>11.454952</v>
+        <v>11.4309514</v>
       </c>
       <c r="O82">
-        <v>3.4364856</v>
+        <v>3.42928542</v>
       </c>
       <c r="P82">
-        <v>8.018466399999999</v>
+        <v>8.00166598</v>
       </c>
       <c r="Q82">
-        <v>11.0184664</v>
+        <v>11.00166598</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3820509535835451</v>
+        <v>0.398351207566127</v>
       </c>
       <c r="T82">
-        <v>2.344490457873503</v>
+        <v>2.458143042396457</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>6.96597168404123</v>
+        <v>6.879972033620969</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1064748294375641</v>
+        <v>0.1061314681584192</v>
       </c>
       <c r="C83">
-        <v>30.4733135505417</v>
+        <v>30.36633058186784</v>
       </c>
       <c r="D83">
-        <v>58.86531355054171</v>
+        <v>59.20033058186785</v>
       </c>
       <c r="E83">
-        <v>16.90200000000001</v>
+        <v>17.34400000000001</v>
       </c>
       <c r="F83">
-        <v>35.80200000000001</v>
+        <v>36.24400000000001</v>
       </c>
       <c r="G83">
         <v>7.41</v>
@@ -8093,28 +8093,28 @@
         <v>13.375</v>
       </c>
       <c r="M83">
-        <v>1.9440486</v>
+        <v>1.9680492</v>
       </c>
       <c r="N83">
-        <v>11.4309514</v>
+        <v>11.4069508</v>
       </c>
       <c r="O83">
-        <v>3.42928542</v>
+        <v>3.422085239999999</v>
       </c>
       <c r="P83">
-        <v>8.00166598</v>
+        <v>7.984865559999999</v>
       </c>
       <c r="Q83">
-        <v>11.00166598</v>
+        <v>10.98486556</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.398351207566127</v>
+        <v>0.4164626008801068</v>
       </c>
       <c r="T83">
-        <v>2.458143042396457</v>
+        <v>2.584423691866406</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>6.879972033620969</v>
+        <v>6.796069935649981</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1061314681584192</v>
+        <v>0.1057881068792743</v>
       </c>
       <c r="C84">
-        <v>30.36633058186784</v>
+        <v>30.26318276927391</v>
       </c>
       <c r="D84">
-        <v>59.20033058186785</v>
+        <v>59.53918276927392</v>
       </c>
       <c r="E84">
-        <v>17.34400000000001</v>
+        <v>17.78600000000001</v>
       </c>
       <c r="F84">
-        <v>36.24400000000001</v>
+        <v>36.68600000000001</v>
       </c>
       <c r="G84">
         <v>7.41</v>
@@ -8175,28 +8175,28 @@
         <v>13.375</v>
       </c>
       <c r="M84">
-        <v>1.9680492</v>
+        <v>1.9920498</v>
       </c>
       <c r="N84">
-        <v>11.4069508</v>
+        <v>11.3829502</v>
       </c>
       <c r="O84">
-        <v>3.422085239999999</v>
+        <v>3.41488506</v>
       </c>
       <c r="P84">
-        <v>7.984865559999999</v>
+        <v>7.96806514</v>
       </c>
       <c r="Q84">
-        <v>10.98486556</v>
+        <v>10.96806514</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4164626008801068</v>
+        <v>0.4367047463486725</v>
       </c>
       <c r="T84">
-        <v>2.584423691866406</v>
+        <v>2.725560888332819</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.796069935649981</v>
+        <v>6.7141895749795</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1057881068792743</v>
+        <v>0.1054447456001294</v>
       </c>
       <c r="C85">
-        <v>30.26318276927391</v>
+        <v>30.16393634713233</v>
       </c>
       <c r="D85">
-        <v>59.53918276927392</v>
+        <v>59.88193634713234</v>
       </c>
       <c r="E85">
-        <v>17.78600000000001</v>
+        <v>18.22800000000001</v>
       </c>
       <c r="F85">
-        <v>36.68600000000001</v>
+        <v>37.12800000000001</v>
       </c>
       <c r="G85">
         <v>7.41</v>
@@ -8257,28 +8257,28 @@
         <v>13.375</v>
       </c>
       <c r="M85">
-        <v>1.9920498</v>
+        <v>2.016050400000001</v>
       </c>
       <c r="N85">
-        <v>11.3829502</v>
+        <v>11.3589496</v>
       </c>
       <c r="O85">
-        <v>3.41488506</v>
+        <v>3.40768488</v>
       </c>
       <c r="P85">
-        <v>7.96806514</v>
+        <v>7.951264719999999</v>
       </c>
       <c r="Q85">
-        <v>10.96806514</v>
+        <v>10.95126472</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4367047463486725</v>
+        <v>0.459477160000809</v>
       </c>
       <c r="T85">
-        <v>2.725560888332819</v>
+        <v>2.884340234357534</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.7141895749795</v>
+        <v>6.634258746705934</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1054447456001294</v>
+        <v>0.1051013843209845</v>
       </c>
       <c r="C86">
-        <v>30.16393634713233</v>
+        <v>30.06865908383156</v>
       </c>
       <c r="D86">
-        <v>59.88193634713234</v>
+        <v>60.22865908383156</v>
       </c>
       <c r="E86">
-        <v>18.228</v>
+        <v>18.67</v>
       </c>
       <c r="F86">
-        <v>37.128</v>
+        <v>37.57</v>
       </c>
       <c r="G86">
         <v>7.41</v>
@@ -8339,28 +8339,28 @@
         <v>13.375</v>
       </c>
       <c r="M86">
-        <v>2.0160504</v>
+        <v>2.040051</v>
       </c>
       <c r="N86">
-        <v>11.3589496</v>
+        <v>11.334949</v>
       </c>
       <c r="O86">
-        <v>3.40768488</v>
+        <v>3.4004847</v>
       </c>
       <c r="P86">
-        <v>7.951264719999999</v>
+        <v>7.9344643</v>
       </c>
       <c r="Q86">
-        <v>10.95126472</v>
+        <v>10.9344643</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4594771600008087</v>
+        <v>0.4852858954732299</v>
       </c>
       <c r="T86">
-        <v>2.884340234357532</v>
+        <v>3.064290159852209</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.634258746705934</v>
+        <v>6.556208643803513</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1051013843209845</v>
+        <v>0.1047580230418396</v>
       </c>
       <c r="C87">
-        <v>30.06865908383156</v>
+        <v>29.97742032644534</v>
       </c>
       <c r="D87">
-        <v>60.22865908383156</v>
+        <v>60.57942032644534</v>
       </c>
       <c r="E87">
-        <v>18.67</v>
+        <v>19.112</v>
       </c>
       <c r="F87">
-        <v>37.57</v>
+        <v>38.012</v>
       </c>
       <c r="G87">
         <v>7.41</v>
@@ -8421,28 +8421,28 @@
         <v>13.375</v>
       </c>
       <c r="M87">
-        <v>2.040051</v>
+        <v>2.0640516</v>
       </c>
       <c r="N87">
-        <v>11.334949</v>
+        <v>11.3109484</v>
       </c>
       <c r="O87">
-        <v>3.4004847</v>
+        <v>3.39328452</v>
       </c>
       <c r="P87">
-        <v>7.9344643</v>
+        <v>7.917663880000001</v>
       </c>
       <c r="Q87">
-        <v>10.9344643</v>
+        <v>10.91766388</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4852858954732299</v>
+        <v>0.514781593155997</v>
       </c>
       <c r="T87">
-        <v>3.064290159852209</v>
+        <v>3.269947217560411</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.556208643803513</v>
+        <v>6.47997365957324</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1047580230418396</v>
+        <v>0.1044146617626947</v>
       </c>
       <c r="C88">
-        <v>29.97742032644534</v>
+        <v>29.89029104697187</v>
       </c>
       <c r="D88">
-        <v>60.57942032644534</v>
+        <v>60.93429104697188</v>
       </c>
       <c r="E88">
-        <v>19.112</v>
+        <v>19.554</v>
       </c>
       <c r="F88">
-        <v>38.012</v>
+        <v>38.454</v>
       </c>
       <c r="G88">
         <v>7.41</v>
@@ -8503,28 +8503,28 @@
         <v>13.375</v>
       </c>
       <c r="M88">
-        <v>2.0640516</v>
+        <v>2.0880522</v>
       </c>
       <c r="N88">
-        <v>11.3109484</v>
+        <v>11.2869478</v>
       </c>
       <c r="O88">
-        <v>3.39328452</v>
+        <v>3.38608434</v>
       </c>
       <c r="P88">
-        <v>7.917663880000001</v>
+        <v>7.90086346</v>
       </c>
       <c r="Q88">
-        <v>10.91766388</v>
+        <v>10.90086346</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.514781593155997</v>
+        <v>0.5488150904822667</v>
       </c>
       <c r="T88">
-        <v>3.269947217560411</v>
+        <v>3.507243822608336</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.47997365957324</v>
+        <v>6.405491203716076</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1044146617626947</v>
+        <v>0.1040713004835498</v>
       </c>
       <c r="C89">
-        <v>29.89029104697187</v>
+        <v>29.80734389020782</v>
       </c>
       <c r="D89">
-        <v>60.93429104697188</v>
+        <v>61.29334389020782</v>
       </c>
       <c r="E89">
-        <v>19.554</v>
+        <v>19.996</v>
       </c>
       <c r="F89">
-        <v>38.454</v>
+        <v>38.896</v>
       </c>
       <c r="G89">
         <v>7.41</v>
@@ -8585,28 +8585,28 @@
         <v>13.375</v>
       </c>
       <c r="M89">
-        <v>2.0880522</v>
+        <v>2.1120528</v>
       </c>
       <c r="N89">
-        <v>11.2869478</v>
+        <v>11.2629472</v>
       </c>
       <c r="O89">
-        <v>3.38608434</v>
+        <v>3.37888416</v>
       </c>
       <c r="P89">
-        <v>7.90086346</v>
+        <v>7.884063039999999</v>
       </c>
       <c r="Q89">
-        <v>10.90086346</v>
+        <v>10.88406304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5488150904822667</v>
+        <v>0.5885208373629149</v>
       </c>
       <c r="T89">
-        <v>3.507243822608336</v>
+        <v>3.784089861830917</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.405491203716076</v>
+        <v>6.332701530946574</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1040713004835498</v>
+        <v>0.1037279392044049</v>
       </c>
       <c r="C90">
-        <v>29.80734389020782</v>
+        <v>29.7286532233251</v>
       </c>
       <c r="D90">
-        <v>61.29334389020782</v>
+        <v>61.6566532233251</v>
       </c>
       <c r="E90">
-        <v>19.996</v>
+        <v>20.438</v>
       </c>
       <c r="F90">
-        <v>38.896</v>
+        <v>39.338</v>
       </c>
       <c r="G90">
         <v>7.41</v>
@@ -8667,28 +8667,28 @@
         <v>13.375</v>
       </c>
       <c r="M90">
-        <v>2.1120528</v>
+        <v>2.1360534</v>
       </c>
       <c r="N90">
-        <v>11.2629472</v>
+        <v>11.2389466</v>
       </c>
       <c r="O90">
-        <v>3.37888416</v>
+        <v>3.37168398</v>
       </c>
       <c r="P90">
-        <v>7.884063039999999</v>
+        <v>7.86726262</v>
       </c>
       <c r="Q90">
-        <v>10.88406304</v>
+        <v>10.86726262</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5885208373629149</v>
+        <v>0.6354458109491353</v>
       </c>
       <c r="T90">
-        <v>3.784089861830917</v>
+        <v>4.111271544548511</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.332701530946574</v>
+        <v>6.261547581160658</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1037279392044049</v>
+        <v>0.10338457792526</v>
       </c>
       <c r="C91">
-        <v>29.7286532233251</v>
+        <v>29.65429518722094</v>
       </c>
       <c r="D91">
-        <v>61.6566532233251</v>
+        <v>62.02429518722094</v>
       </c>
       <c r="E91">
-        <v>20.438</v>
+        <v>20.88</v>
       </c>
       <c r="F91">
-        <v>39.338</v>
+        <v>39.78</v>
       </c>
       <c r="G91">
         <v>7.41</v>
@@ -8749,28 +8749,28 @@
         <v>13.375</v>
       </c>
       <c r="M91">
-        <v>2.1360534</v>
+        <v>2.160054</v>
       </c>
       <c r="N91">
-        <v>11.2389466</v>
+        <v>11.214946</v>
       </c>
       <c r="O91">
-        <v>3.37168398</v>
+        <v>3.3644838</v>
       </c>
       <c r="P91">
-        <v>7.86726262</v>
+        <v>7.850462199999999</v>
       </c>
       <c r="Q91">
-        <v>10.86726262</v>
+        <v>10.8504622</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6354458109491353</v>
+        <v>0.6917557792525998</v>
       </c>
       <c r="T91">
-        <v>4.111271544548511</v>
+        <v>4.503889563809624</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.261547581160658</v>
+        <v>6.191974830258872</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.10338457792526</v>
+        <v>0.1030412166461151</v>
       </c>
       <c r="C92">
-        <v>29.65429518722094</v>
+        <v>29.58434774971638</v>
       </c>
       <c r="D92">
-        <v>62.02429518722094</v>
+        <v>62.39634774971638</v>
       </c>
       <c r="E92">
-        <v>20.88</v>
+        <v>21.322</v>
       </c>
       <c r="F92">
-        <v>39.78</v>
+        <v>40.222</v>
       </c>
       <c r="G92">
         <v>7.41</v>
@@ -8831,28 +8831,28 @@
         <v>13.375</v>
       </c>
       <c r="M92">
-        <v>2.160054</v>
+        <v>2.1840546</v>
       </c>
       <c r="N92">
-        <v>11.214946</v>
+        <v>11.1909454</v>
       </c>
       <c r="O92">
-        <v>3.3644838</v>
+        <v>3.35728362</v>
       </c>
       <c r="P92">
-        <v>7.850462199999999</v>
+        <v>7.83366178</v>
       </c>
       <c r="Q92">
-        <v>10.8504622</v>
+        <v>10.83366178</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6917557792525998</v>
+        <v>0.7605790738457232</v>
       </c>
       <c r="T92">
-        <v>4.503889563809624</v>
+        <v>4.983756031795429</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.191974830258872</v>
+        <v>6.123931150805479</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1030412166461151</v>
+        <v>0.1033418553669702</v>
       </c>
       <c r="C93">
-        <v>29.58434774971638</v>
+        <v>28.81634578030003</v>
       </c>
       <c r="D93">
-        <v>62.39634774971638</v>
+        <v>62.07034578030002</v>
       </c>
       <c r="E93">
-        <v>21.322</v>
+        <v>21.764</v>
       </c>
       <c r="F93">
-        <v>40.222</v>
+        <v>40.664</v>
       </c>
       <c r="G93">
         <v>7.41</v>
@@ -8913,45 +8913,45 @@
         <v>13.375</v>
       </c>
       <c r="M93">
-        <v>2.1840546</v>
+        <v>2.2487192</v>
       </c>
       <c r="N93">
-        <v>11.1909454</v>
+        <v>11.1262808</v>
       </c>
       <c r="O93">
-        <v>3.35728362</v>
+        <v>3.33788424</v>
       </c>
       <c r="P93">
-        <v>7.83366178</v>
+        <v>7.788396560000001</v>
       </c>
       <c r="Q93">
-        <v>10.83366178</v>
+        <v>10.78839656</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7605790738457232</v>
+        <v>0.8466081920871275</v>
       </c>
       <c r="T93">
-        <v>4.983756031795429</v>
+        <v>5.583589116777686</v>
       </c>
       <c r="U93">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V93">
         <v>0.3</v>
       </c>
       <c r="W93">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>6.123931150805479</v>
+        <v>5.94783021375012</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1033418553669702</v>
+        <v>0.1030054940878253</v>
       </c>
       <c r="C94">
-        <v>28.81634578030003</v>
+        <v>28.73931178988601</v>
       </c>
       <c r="D94">
-        <v>62.07034578030002</v>
+        <v>62.43531178988601</v>
       </c>
       <c r="E94">
-        <v>21.764</v>
+        <v>22.206</v>
       </c>
       <c r="F94">
-        <v>40.664</v>
+        <v>41.106</v>
       </c>
       <c r="G94">
         <v>7.41</v>
@@ -8995,28 +8995,28 @@
         <v>13.375</v>
       </c>
       <c r="M94">
-        <v>2.2487192</v>
+        <v>2.2731618</v>
       </c>
       <c r="N94">
-        <v>11.1262808</v>
+        <v>11.1018382</v>
       </c>
       <c r="O94">
-        <v>3.33788424</v>
+        <v>3.33055146</v>
       </c>
       <c r="P94">
-        <v>7.788396560000001</v>
+        <v>7.77128674</v>
       </c>
       <c r="Q94">
-        <v>10.78839656</v>
+        <v>10.77128674</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8466081920871275</v>
+        <v>0.9572170583975043</v>
       </c>
       <c r="T94">
-        <v>5.583589116777686</v>
+        <v>6.354803083183445</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.94783021375012</v>
+        <v>5.883875050161409</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1030054940878253</v>
+        <v>0.1026691328086804</v>
       </c>
       <c r="C95">
-        <v>28.73931178988601</v>
+        <v>28.66659509526201</v>
       </c>
       <c r="D95">
-        <v>62.43531178988601</v>
+        <v>62.80459509526202</v>
       </c>
       <c r="E95">
-        <v>22.206</v>
+        <v>22.648</v>
       </c>
       <c r="F95">
-        <v>41.106</v>
+        <v>41.548</v>
       </c>
       <c r="G95">
         <v>7.41</v>
@@ -9077,28 +9077,28 @@
         <v>13.375</v>
       </c>
       <c r="M95">
-        <v>2.2731618</v>
+        <v>2.2976044</v>
       </c>
       <c r="N95">
-        <v>11.1018382</v>
+        <v>11.0773956</v>
       </c>
       <c r="O95">
-        <v>3.33055146</v>
+        <v>3.32321868</v>
       </c>
       <c r="P95">
-        <v>7.77128674</v>
+        <v>7.754176919999999</v>
       </c>
       <c r="Q95">
-        <v>10.77128674</v>
+        <v>10.75417692</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9572170583975043</v>
+        <v>1.10469554681134</v>
       </c>
       <c r="T95">
-        <v>6.354803083183445</v>
+        <v>7.383088371724457</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.883875050161409</v>
+        <v>5.82128063473416</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1026691328086804</v>
+        <v>0.1023327715295355</v>
       </c>
       <c r="C96">
-        <v>28.66659509526201</v>
+        <v>28.59827275816205</v>
       </c>
       <c r="D96">
-        <v>62.80459509526202</v>
+        <v>63.17827275816207</v>
       </c>
       <c r="E96">
-        <v>22.648</v>
+        <v>23.09000000000001</v>
       </c>
       <c r="F96">
-        <v>41.548</v>
+        <v>41.99000000000001</v>
       </c>
       <c r="G96">
         <v>7.41</v>
@@ -9159,28 +9159,28 @@
         <v>13.375</v>
       </c>
       <c r="M96">
-        <v>2.2976044</v>
+        <v>2.322047</v>
       </c>
       <c r="N96">
-        <v>11.0773956</v>
+        <v>11.052953</v>
       </c>
       <c r="O96">
-        <v>3.32321868</v>
+        <v>3.3158859</v>
       </c>
       <c r="P96">
-        <v>7.754176919999999</v>
+        <v>7.737067099999999</v>
       </c>
       <c r="Q96">
-        <v>10.75417692</v>
+        <v>10.7370671</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.10469554681134</v>
+        <v>1.311165430590711</v>
       </c>
       <c r="T96">
-        <v>7.383088371724457</v>
+        <v>8.822687775681876</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.82128063473416</v>
+        <v>5.7600039964738</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1023327715295355</v>
+        <v>0.1019964102503906</v>
       </c>
       <c r="C97">
-        <v>28.59827275816205</v>
+        <v>28.53442368531943</v>
       </c>
       <c r="D97">
-        <v>63.17827275816207</v>
+        <v>63.55642368531944</v>
       </c>
       <c r="E97">
-        <v>23.09000000000001</v>
+        <v>23.53200000000001</v>
       </c>
       <c r="F97">
-        <v>41.99000000000001</v>
+        <v>42.43200000000001</v>
       </c>
       <c r="G97">
         <v>7.41</v>
@@ -9241,28 +9241,28 @@
         <v>13.375</v>
       </c>
       <c r="M97">
-        <v>2.322047</v>
+        <v>2.3464896</v>
       </c>
       <c r="N97">
-        <v>11.052953</v>
+        <v>11.0285104</v>
       </c>
       <c r="O97">
-        <v>3.3158859</v>
+        <v>3.30855312</v>
       </c>
       <c r="P97">
-        <v>7.737067099999999</v>
+        <v>7.71995728</v>
       </c>
       <c r="Q97">
-        <v>10.7370671</v>
+        <v>10.71995728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.311165430590711</v>
+        <v>1.620870256259767</v>
       </c>
       <c r="T97">
-        <v>8.822687775681876</v>
+        <v>10.98208688161801</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.7600039964738</v>
+        <v>5.700003954843865</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1019964102503906</v>
+        <v>0.1016600489712456</v>
       </c>
       <c r="C98">
-        <v>28.53442368531942</v>
+        <v>28.47512868401491</v>
       </c>
       <c r="D98">
-        <v>63.55642368531942</v>
+        <v>63.93912868401492</v>
       </c>
       <c r="E98">
-        <v>23.532</v>
+        <v>23.974</v>
       </c>
       <c r="F98">
-        <v>42.432</v>
+        <v>42.874</v>
       </c>
       <c r="G98">
         <v>7.41</v>
@@ -9323,28 +9323,28 @@
         <v>13.375</v>
       </c>
       <c r="M98">
-        <v>2.3464896</v>
+        <v>2.3709322</v>
       </c>
       <c r="N98">
-        <v>11.0285104</v>
+        <v>11.0040678</v>
       </c>
       <c r="O98">
-        <v>3.30855312</v>
+        <v>3.30122034</v>
       </c>
       <c r="P98">
-        <v>7.71995728</v>
+        <v>7.702847459999999</v>
       </c>
       <c r="Q98">
-        <v>10.71995728</v>
+        <v>10.70284746</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.620870256259763</v>
+        <v>2.137044965708187</v>
       </c>
       <c r="T98">
-        <v>10.98208688161798</v>
+        <v>14.58108539151151</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.700003954843865</v>
+        <v>5.64124102747434</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1016600489712456</v>
+        <v>0.1013236876921007</v>
       </c>
       <c r="C99">
-        <v>28.47512868401491</v>
+        <v>28.42047051964421</v>
       </c>
       <c r="D99">
-        <v>63.93912868401492</v>
+        <v>64.32647051964422</v>
       </c>
       <c r="E99">
-        <v>23.974</v>
+        <v>24.416</v>
       </c>
       <c r="F99">
-        <v>42.874</v>
+        <v>43.316</v>
       </c>
       <c r="G99">
         <v>7.41</v>
@@ -9405,28 +9405,28 @@
         <v>13.375</v>
       </c>
       <c r="M99">
-        <v>2.3709322</v>
+        <v>2.3953748</v>
       </c>
       <c r="N99">
-        <v>11.0040678</v>
+        <v>10.9796252</v>
       </c>
       <c r="O99">
-        <v>3.30122034</v>
+        <v>3.293887559999999</v>
       </c>
       <c r="P99">
-        <v>7.702847459999999</v>
+        <v>7.685737639999999</v>
       </c>
       <c r="Q99">
-        <v>10.70284746</v>
+        <v>10.68573764</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.137044965708187</v>
+        <v>3.169394384605035</v>
       </c>
       <c r="T99">
-        <v>14.58108539151151</v>
+        <v>21.77908241129857</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.64124102747434</v>
+        <v>5.58367734352052</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1013236876921007</v>
+        <v>0.1009873264129559</v>
       </c>
       <c r="C100">
-        <v>28.42047051964421</v>
+        <v>28.37053397539052</v>
       </c>
       <c r="D100">
-        <v>64.32647051964422</v>
+        <v>64.71853397539053</v>
       </c>
       <c r="E100">
-        <v>24.416</v>
+        <v>24.858</v>
       </c>
       <c r="F100">
-        <v>43.316</v>
+        <v>43.758</v>
       </c>
       <c r="G100">
         <v>7.41</v>
@@ -9487,28 +9487,28 @@
         <v>13.375</v>
       </c>
       <c r="M100">
-        <v>2.3953748</v>
+        <v>2.4198174</v>
       </c>
       <c r="N100">
-        <v>10.9796252</v>
+        <v>10.9551826</v>
       </c>
       <c r="O100">
-        <v>3.293887559999999</v>
+        <v>3.28655478</v>
       </c>
       <c r="P100">
-        <v>7.685737639999999</v>
+        <v>7.668627820000001</v>
       </c>
       <c r="Q100">
-        <v>10.68573764</v>
+        <v>10.66862782</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.169394384605035</v>
+        <v>6.266442641295579</v>
       </c>
       <c r="T100">
-        <v>21.77908241129857</v>
+        <v>43.37307347065976</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.58367734352052</v>
+        <v>5.527276562272839</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1009873264129559</v>
-      </c>
-      <c r="C101">
-        <v>28.37053397539052</v>
-      </c>
-      <c r="D101">
-        <v>64.71853397539053</v>
-      </c>
-      <c r="E101">
-        <v>24.858</v>
-      </c>
-      <c r="F101">
-        <v>43.758</v>
-      </c>
-      <c r="G101">
-        <v>7.41</v>
-      </c>
-      <c r="H101">
-        <v>25.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.375</v>
-      </c>
-      <c r="K101">
-        <v>3</v>
-      </c>
-      <c r="L101">
-        <v>13.375</v>
-      </c>
-      <c r="M101">
-        <v>2.4198174</v>
-      </c>
-      <c r="N101">
-        <v>10.9551826</v>
-      </c>
-      <c r="O101">
-        <v>3.28655478</v>
-      </c>
-      <c r="P101">
-        <v>7.668627820000001</v>
-      </c>
-      <c r="Q101">
-        <v>10.66862782</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.266442641295579</v>
-      </c>
-      <c r="T101">
-        <v>43.37307347065976</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.527276562272839</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
